--- a/menu/Ciao_Fiyat_Listesi.xlsx
+++ b/menu/Ciao_Fiyat_Listesi.xlsx
@@ -668,7 +668,7 @@
     <t xml:space="preserve">Soda</t>
   </si>
   <si>
-    <t xml:space="preserve">Premium Soda</t>
+    <t xml:space="preserve">San Pellegrino</t>
   </si>
   <si>
     <t xml:space="preserve">Limonata</t>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C59" s="24"/>
       <c r="D59" s="25" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E59" s="25"/>
       <c r="F59" s="36"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C60" s="24"/>
       <c r="D60" s="25" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E60" s="25"/>
       <c r="F60" s="36"/>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="C61" s="24"/>
       <c r="D61" s="25" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E61" s="25"/>
       <c r="F61" s="36"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="C62" s="24"/>
       <c r="D62" s="25" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="E62" s="25"/>
       <c r="F62" s="36"/>
@@ -7154,7 +7154,7 @@
       <c r="F85" s="45"/>
       <c r="G85" s="47" t="n">
         <f aca="false">IF(Soğuklar!D59="","",Soğuklar!D59)</f>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H85" s="47"/>
       <c r="I85" s="47"/>
@@ -7163,7 +7163,7 @@
       <c r="L85" s="45"/>
       <c r="M85" s="48" t="n">
         <f aca="false">IF(COUNT(G85:I85)=0,"",MIN(G85:I85))</f>
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7180,7 +7180,7 @@
       <c r="F86" s="45"/>
       <c r="G86" s="47" t="n">
         <f aca="false">IF(Soğuklar!D60="","",Soğuklar!D60)</f>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H86" s="47"/>
       <c r="I86" s="47"/>
@@ -7189,7 +7189,7 @@
       <c r="L86" s="45"/>
       <c r="M86" s="48" t="n">
         <f aca="false">IF(COUNT(G86:I86)=0,"",MIN(G86:I86))</f>
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7206,7 +7206,7 @@
       <c r="F87" s="45"/>
       <c r="G87" s="47" t="n">
         <f aca="false">IF(Soğuklar!D61="","",Soğuklar!D61)</f>
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="H87" s="47"/>
       <c r="I87" s="47"/>
@@ -7215,7 +7215,7 @@
       <c r="L87" s="45"/>
       <c r="M87" s="48" t="n">
         <f aca="false">IF(COUNT(G87:I87)=0,"",MIN(G87:I87))</f>
-        <v>100</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7232,7 +7232,7 @@
       <c r="F88" s="45"/>
       <c r="G88" s="47" t="n">
         <f aca="false">IF(Soğuklar!D62="","",Soğuklar!D62)</f>
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="H88" s="47"/>
       <c r="I88" s="47"/>
@@ -7241,7 +7241,7 @@
       <c r="L88" s="45"/>
       <c r="M88" s="48" t="n">
         <f aca="false">IF(COUNT(G88:I88)=0,"",MIN(G88:I88))</f>
-        <v>130</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/menu/Ciao_Fiyat_Listesi.xlsx
+++ b/menu/Ciao_Fiyat_Listesi.xlsx
@@ -18,11 +18,11 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">'Kasa Önü'!$5:$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Simpra Menü'!$B$5:$J$176</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Simpra Menü'!$B$5:$J$177</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Sıcaklar!$5:$5</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Soğuklar!$5:$5</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'Tatlı &amp; Atıştırmalık'!$5:$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Tüm Ürünler (POS)'!$B$5:$M$109</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Tüm Ürünler (POS)'!$B$5:$M$110</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="350">
   <si>
     <t xml:space="preserve">MENÜ FİYAT LİSTESİ</t>
   </si>
@@ -723,21 +723,21 @@
     <t xml:space="preserve">Berry World</t>
   </si>
   <si>
+    <t xml:space="preserve">Orman Meyveli Cheesecake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bisküvi taban · Orman meyveleri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blueberry</t>
+  </si>
+  <si>
     <t xml:space="preserve">Orman Meyveli Pasta</t>
   </si>
   <si>
     <t xml:space="preserve">Pandispanya · Krema · Orman meyveleri</t>
   </si>
   <si>
-    <t xml:space="preserve">Blueberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yaban Mersinli Cheesecake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bisküvi taban · Yaban mersini</t>
-  </si>
-  <si>
     <t xml:space="preserve">Italian Mood</t>
   </si>
   <si>
@@ -811,6 +811,15 @@
   </si>
   <si>
     <t xml:space="preserve">Choux · Vanilyalı krema · Çikolata sos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cookielaton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Çikolatalı Cookie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitter ve sütlü çikolata parçaları</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud 9</t>
@@ -2272,23 +2281,23 @@
         <v>8</v>
       </c>
       <c r="C6" s="7" t="n">
-        <f aca="false">COUNTIF('Tüm Ürünler (POS)'!$B$6:$B$109,B6)</f>
+        <f aca="false">COUNTIF('Tüm Ürünler (POS)'!$B$6:$B$110,B6)</f>
         <v>44</v>
       </c>
       <c r="D6" s="7" t="n">
-        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$109,B6,'Tüm Ürünler (POS)'!$J$6:$J$109,"Evet")</f>
+        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$110,B6,'Tüm Ürünler (POS)'!$J$6:$J$110,"Evet")</f>
         <v>9</v>
       </c>
       <c r="E6" s="8" t="n">
-        <f aca="false">_xlfn.MINIFS('Tüm Ürünler (POS)'!$M$6:$M$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B6)</f>
+        <f aca="false">_xlfn.MINIFS('Tüm Ürünler (POS)'!$M$6:$M$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B6)</f>
         <v>70</v>
       </c>
       <c r="F6" s="8" t="n">
-        <f aca="false">MAX(_xlfn.MAXIFS('Tüm Ürünler (POS)'!$G$6:$G$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B6),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$H$6:$H$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B6),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$I$6:$I$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B6))</f>
+        <f aca="false">MAX(_xlfn.MAXIFS('Tüm Ürünler (POS)'!$G$6:$G$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B6),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$H$6:$H$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B6),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$I$6:$I$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B6))</f>
         <v>340</v>
       </c>
       <c r="G6" s="7" t="n">
-        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$109,B6,'Tüm Ürünler (POS)'!$L$6:$L$109,"*Fiyat girilecek*")</f>
+        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$110,B6,'Tüm Ürünler (POS)'!$L$6:$L$110,"*Fiyat girilecek*")</f>
         <v>0</v>
       </c>
     </row>
@@ -2297,23 +2306,23 @@
         <v>9</v>
       </c>
       <c r="C7" s="7" t="n">
-        <f aca="false">COUNTIF('Tüm Ürünler (POS)'!$B$6:$B$109,B7)</f>
+        <f aca="false">COUNTIF('Tüm Ürünler (POS)'!$B$6:$B$110,B7)</f>
         <v>40</v>
       </c>
       <c r="D7" s="7" t="n">
-        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$109,B7,'Tüm Ürünler (POS)'!$J$6:$J$109,"Evet")</f>
+        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$110,B7,'Tüm Ürünler (POS)'!$J$6:$J$110,"Evet")</f>
         <v>8</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">_xlfn.MINIFS('Tüm Ürünler (POS)'!$M$6:$M$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B7)</f>
+        <f aca="false">_xlfn.MINIFS('Tüm Ürünler (POS)'!$M$6:$M$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B7)</f>
         <v>40</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">MAX(_xlfn.MAXIFS('Tüm Ürünler (POS)'!$G$6:$G$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B7),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$H$6:$H$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B7),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$I$6:$I$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B7))</f>
+        <f aca="false">MAX(_xlfn.MAXIFS('Tüm Ürünler (POS)'!$G$6:$G$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B7),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$H$6:$H$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B7),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$I$6:$I$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B7))</f>
         <v>350</v>
       </c>
       <c r="G7" s="7" t="n">
-        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$109,B7,'Tüm Ürünler (POS)'!$L$6:$L$109,"*Fiyat girilecek*")</f>
+        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$110,B7,'Tüm Ürünler (POS)'!$L$6:$L$110,"*Fiyat girilecek*")</f>
         <v>0</v>
       </c>
     </row>
@@ -2322,23 +2331,23 @@
         <v>10</v>
       </c>
       <c r="C8" s="7" t="n">
-        <f aca="false">COUNTIF('Tüm Ürünler (POS)'!$B$6:$B$109,B8)</f>
-        <v>16</v>
+        <f aca="false">COUNTIF('Tüm Ürünler (POS)'!$B$6:$B$110,B8)</f>
+        <v>17</v>
       </c>
       <c r="D8" s="7" t="n">
-        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$109,B8,'Tüm Ürünler (POS)'!$J$6:$J$109,"Evet")</f>
+        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$110,B8,'Tüm Ürünler (POS)'!$J$6:$J$110,"Evet")</f>
         <v>3</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">_xlfn.MINIFS('Tüm Ürünler (POS)'!$M$6:$M$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B8)</f>
+        <f aca="false">_xlfn.MINIFS('Tüm Ürünler (POS)'!$M$6:$M$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B8)</f>
         <v>170</v>
       </c>
       <c r="F8" s="8" t="n">
-        <f aca="false">MAX(_xlfn.MAXIFS('Tüm Ürünler (POS)'!$G$6:$G$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B8),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$H$6:$H$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B8),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$I$6:$I$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B8))</f>
+        <f aca="false">MAX(_xlfn.MAXIFS('Tüm Ürünler (POS)'!$G$6:$G$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B8),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$H$6:$H$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B8),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$I$6:$I$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B8))</f>
         <v>320</v>
       </c>
       <c r="G8" s="7" t="n">
-        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$109,B8,'Tüm Ürünler (POS)'!$L$6:$L$109,"*Fiyat girilecek*")</f>
+        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$110,B8,'Tüm Ürünler (POS)'!$L$6:$L$110,"*Fiyat girilecek*")</f>
         <v>2</v>
       </c>
     </row>
@@ -2347,23 +2356,23 @@
         <v>11</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">COUNTIF('Tüm Ürünler (POS)'!$B$6:$B$109,B9)</f>
+        <f aca="false">COUNTIF('Tüm Ürünler (POS)'!$B$6:$B$110,B9)</f>
         <v>4</v>
       </c>
       <c r="D9" s="7" t="n">
-        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$109,B9,'Tüm Ürünler (POS)'!$J$6:$J$109,"Evet")</f>
+        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$110,B9,'Tüm Ürünler (POS)'!$J$6:$J$110,"Evet")</f>
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <f aca="false">_xlfn.MINIFS('Tüm Ürünler (POS)'!$M$6:$M$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B9)</f>
+        <f aca="false">_xlfn.MINIFS('Tüm Ürünler (POS)'!$M$6:$M$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B9)</f>
         <v>190</v>
       </c>
       <c r="F9" s="8" t="n">
-        <f aca="false">MAX(_xlfn.MAXIFS('Tüm Ürünler (POS)'!$G$6:$G$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B9),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$H$6:$H$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B9),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$I$6:$I$109,'Tüm Ürünler (POS)'!$B$6:$B$109,B9))</f>
+        <f aca="false">MAX(_xlfn.MAXIFS('Tüm Ürünler (POS)'!$G$6:$G$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B9),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$H$6:$H$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B9),_xlfn.MAXIFS('Tüm Ürünler (POS)'!$I$6:$I$110,'Tüm Ürünler (POS)'!$B$6:$B$110,B9))</f>
         <v>210</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$109,B9,'Tüm Ürünler (POS)'!$L$6:$L$109,"*Fiyat girilecek*")</f>
+        <f aca="false">COUNTIFS('Tüm Ürünler (POS)'!$B$6:$B$110,B9,'Tüm Ürünler (POS)'!$L$6:$L$110,"*Fiyat girilecek*")</f>
         <v>0</v>
       </c>
     </row>
@@ -2373,7 +2382,7 @@
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">SUM(C6:C9)</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">SUM(D6:D9)</f>
@@ -4392,7 +4401,7 @@
     <tabColor rgb="FF7A3E26"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:G31"/>
+  <dimension ref="B1:G32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -4665,100 +4674,116 @@
         <v>261</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="28"/>
     </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="41" t="s">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="24" t="s">
+      <c r="C22" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="25" t="s">
+      <c r="D22" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="E24" s="26" t="n">
-        <v>200</v>
-      </c>
-      <c r="F24" s="43"/>
-      <c r="G24" s="28"/>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E22" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="28"/>
+    </row>
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C25" s="42"/>
       <c r="D25" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F25" s="43"/>
       <c r="G25" s="28"/>
     </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="24" t="s">
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="24" t="s">
         <v>268</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C26" s="42"/>
+      <c r="D26" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="E26" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="F26" s="43"/>
+      <c r="G26" s="28"/>
+    </row>
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="E28" s="44"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="28" t="s">
-        <v>271</v>
-      </c>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="C29" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="D29" s="25" t="s">
         <v>273</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>274</v>
       </c>
       <c r="E29" s="44"/>
       <c r="F29" s="43"/>
       <c r="G29" s="28" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="32" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="E30" s="44"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="28" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4766,9 +4791,9 @@
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B32:G32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4800,7 +4825,7 @@
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="45"/>
       <c r="C1" s="46" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D1" s="46"/>
       <c r="E1" s="46"/>
@@ -4813,7 +4838,7 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="47" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
@@ -4835,7 +4860,7 @@
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="48" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C7" s="48"/>
       <c r="D7" s="48"/>
@@ -4843,63 +4868,63 @@
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D8" s="26" t="n">
         <v>190</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D9" s="26" t="n">
         <v>190</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D10" s="26" t="n">
         <v>210</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D11" s="26" t="n">
         <v>210</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="48" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C13" s="48"/>
       <c r="D13" s="48"/>
@@ -4910,14 +4935,14 @@
         <v>210</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D14" s="51" t="n">
         <f aca="false">Soğuklar!D58</f>
         <v>40</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4925,14 +4950,14 @@
         <v>211</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D15" s="51" t="n">
         <f aca="false">Soğuklar!D59</f>
         <v>60</v>
       </c>
       <c r="E15" s="50" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4940,14 +4965,14 @@
         <v>212</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D16" s="51" t="n">
         <f aca="false">Soğuklar!D60</f>
         <v>80</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4955,14 +4980,14 @@
         <v>213</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">Soğuklar!D61</f>
         <v>120</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4970,19 +4995,19 @@
         <v>215</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D18" s="51" t="n">
         <f aca="false">Soğuklar!D63</f>
         <v>170</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="32" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5013,7 +5038,7 @@
     <tabColor rgb="FF1A1210"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:M109"/>
+  <dimension ref="B1:M110"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -5031,7 +5056,7 @@
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -5060,7 +5085,7 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -5079,25 +5104,25 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>4</v>
@@ -5106,10 +5131,10 @@
         <v>118</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5513,7 +5538,7 @@
         <v>230</v>
       </c>
       <c r="J17" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K17" s="53"/>
       <c r="L17" s="53"/>
@@ -5685,7 +5710,7 @@
         <v>250</v>
       </c>
       <c r="J22" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K22" s="53"/>
       <c r="L22" s="53"/>
@@ -5755,7 +5780,7 @@
         <v>270</v>
       </c>
       <c r="J24" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K24" s="53"/>
       <c r="L24" s="53"/>
@@ -5927,7 +5952,7 @@
         <v>250</v>
       </c>
       <c r="J29" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K29" s="53"/>
       <c r="L29" s="53"/>
@@ -6099,7 +6124,7 @@
         <v/>
       </c>
       <c r="J34" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K34" s="53"/>
       <c r="L34" s="53"/>
@@ -6439,7 +6464,7 @@
         <v/>
       </c>
       <c r="J44" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K44" s="53"/>
       <c r="L44" s="53"/>
@@ -6475,10 +6500,10 @@
         <v>320</v>
       </c>
       <c r="J45" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K45" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L45" s="53"/>
       <c r="M45" s="56" t="n">
@@ -6514,7 +6539,7 @@
       </c>
       <c r="J46" s="53"/>
       <c r="K46" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L46" s="53"/>
       <c r="M46" s="56" t="n">
@@ -6549,10 +6574,10 @@
         <v>320</v>
       </c>
       <c r="J47" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K47" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L47" s="53"/>
       <c r="M47" s="56" t="n">
@@ -6587,10 +6612,10 @@
         <v>305</v>
       </c>
       <c r="J48" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K48" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L48" s="53"/>
       <c r="M48" s="56" t="n">
@@ -6626,7 +6651,7 @@
       </c>
       <c r="J49" s="53"/>
       <c r="K49" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L49" s="53"/>
       <c r="M49" s="56" t="n">
@@ -6782,7 +6807,7 @@
         <v>280</v>
       </c>
       <c r="J54" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K54" s="53"/>
       <c r="L54" s="53"/>
@@ -6939,7 +6964,7 @@
         <v>190</v>
       </c>
       <c r="J59" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K59" s="53"/>
       <c r="L59" s="53"/>
@@ -7096,7 +7121,7 @@
         <v>280</v>
       </c>
       <c r="J64" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K64" s="53"/>
       <c r="L64" s="53"/>
@@ -7160,7 +7185,7 @@
         <v>300</v>
       </c>
       <c r="J66" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K66" s="53"/>
       <c r="L66" s="53"/>
@@ -7410,7 +7435,7 @@
         <v>290</v>
       </c>
       <c r="J74" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K74" s="53"/>
       <c r="L74" s="53"/>
@@ -7443,7 +7468,7 @@
         <v>320</v>
       </c>
       <c r="J75" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K75" s="53"/>
       <c r="L75" s="53"/>
@@ -7600,10 +7625,10 @@
         <v>320</v>
       </c>
       <c r="J80" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K80" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L80" s="53"/>
       <c r="M80" s="56" t="n">
@@ -7635,13 +7660,13 @@
         <v>300</v>
       </c>
       <c r="J81" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K81" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L81" s="53" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M81" s="56" t="n">
         <f aca="false">IF(COUNT(G81:I81)=0,"",MIN(G81:I81))</f>
@@ -7673,7 +7698,7 @@
       </c>
       <c r="J82" s="53"/>
       <c r="K82" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L82" s="53"/>
       <c r="M82" s="56" t="n">
@@ -7706,7 +7731,7 @@
       </c>
       <c r="J83" s="53"/>
       <c r="K83" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L83" s="53"/>
       <c r="M83" s="56" t="n">
@@ -8013,7 +8038,7 @@
       <c r="H94" s="55"/>
       <c r="I94" s="55"/>
       <c r="J94" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K94" s="53"/>
       <c r="L94" s="53"/>
@@ -8135,7 +8160,7 @@
       <c r="H98" s="55"/>
       <c r="I98" s="55"/>
       <c r="J98" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K98" s="53"/>
       <c r="L98" s="53"/>
@@ -8167,7 +8192,7 @@
       <c r="H99" s="55"/>
       <c r="I99" s="55"/>
       <c r="J99" s="53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K99" s="53"/>
       <c r="L99" s="53"/>
@@ -8224,7 +8249,7 @@
       </c>
       <c r="G101" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E21="","",'Tatlı &amp; Atıştırmalık'!E21)</f>
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="H101" s="55"/>
       <c r="I101" s="55"/>
@@ -8233,7 +8258,7 @@
       <c r="L101" s="53"/>
       <c r="M101" s="56" t="n">
         <f aca="false">IF(COUNT(G101:I101)=0,"",MIN(G101:I101))</f>
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8241,18 +8266,20 @@
         <v>10</v>
       </c>
       <c r="C102" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="D102" s="54" t="s">
         <v>262</v>
       </c>
-      <c r="D102" s="54" t="s">
+      <c r="E102" s="53" t="s">
         <v>263</v>
       </c>
-      <c r="E102" s="53"/>
       <c r="F102" s="53" t="s">
         <v>264</v>
       </c>
       <c r="G102" s="55" t="n">
-        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E24="","",'Tatlı &amp; Atıştırmalık'!E24)</f>
-        <v>200</v>
+        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E22="","",'Tatlı &amp; Atıştırmalık'!E22)</f>
+        <v>170</v>
       </c>
       <c r="H102" s="55"/>
       <c r="I102" s="55"/>
@@ -8261,7 +8288,7 @@
       <c r="L102" s="53"/>
       <c r="M102" s="56" t="n">
         <f aca="false">IF(COUNT(G102:I102)=0,"",MIN(G102:I102))</f>
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8269,18 +8296,18 @@
         <v>10</v>
       </c>
       <c r="C103" s="53" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D103" s="54" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E103" s="53"/>
       <c r="F103" s="53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G103" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E25="","",'Tatlı &amp; Atıştırmalık'!E25)</f>
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H103" s="55"/>
       <c r="I103" s="55"/>
@@ -8289,7 +8316,7 @@
       <c r="L103" s="53"/>
       <c r="M103" s="56" t="n">
         <f aca="false">IF(COUNT(G103:I103)=0,"",MIN(G103:I103))</f>
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8297,31 +8324,27 @@
         <v>10</v>
       </c>
       <c r="C104" s="53" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D104" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="E104" s="53" t="s">
+      <c r="E104" s="53"/>
+      <c r="F104" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="F104" s="53" t="s">
-        <v>270</v>
-      </c>
-      <c r="G104" s="55" t="str">
-        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E28="","",'Tatlı &amp; Atıştırmalık'!E28)</f>
-        <v/>
+      <c r="G104" s="55" t="n">
+        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E26="","",'Tatlı &amp; Atıştırmalık'!E26)</f>
+        <v>250</v>
       </c>
       <c r="H104" s="55"/>
       <c r="I104" s="55"/>
       <c r="J104" s="53"/>
       <c r="K104" s="53"/>
-      <c r="L104" s="53" t="s">
-        <v>271</v>
-      </c>
-      <c r="M104" s="56" t="str">
+      <c r="L104" s="53"/>
+      <c r="M104" s="56" t="n">
         <f aca="false">IF(COUNT(G104:I104)=0,"",MIN(G104:I104))</f>
-        <v/>
+        <v>250</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8329,16 +8352,16 @@
         <v>10</v>
       </c>
       <c r="C105" s="53" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D105" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="E105" s="53" t="s">
         <v>272</v>
       </c>
-      <c r="E105" s="53" t="s">
+      <c r="F105" s="53" t="s">
         <v>273</v>
-      </c>
-      <c r="F105" s="53" t="s">
-        <v>274</v>
       </c>
       <c r="G105" s="55" t="str">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E29="","",'Tatlı &amp; Atıştırmalık'!E29)</f>
@@ -8349,7 +8372,7 @@
       <c r="J105" s="53"/>
       <c r="K105" s="53"/>
       <c r="L105" s="53" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M105" s="56" t="str">
         <f aca="false">IF(COUNT(G105:I105)=0,"",MIN(G105:I105))</f>
@@ -8358,32 +8381,34 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C106" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="D106" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="E106" s="53" t="s">
+        <v>276</v>
+      </c>
+      <c r="F106" s="53" t="s">
         <v>277</v>
       </c>
-      <c r="D106" s="54" t="s">
-        <v>278</v>
-      </c>
-      <c r="E106" s="53"/>
-      <c r="F106" s="53" t="s">
-        <v>279</v>
-      </c>
-      <c r="G106" s="55" t="n">
-        <f aca="false">IF('Kasa Önü'!D8="","",'Kasa Önü'!D8)</f>
-        <v>190</v>
+      <c r="G106" s="55" t="str">
+        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E30="","",'Tatlı &amp; Atıştırmalık'!E30)</f>
+        <v/>
       </c>
       <c r="H106" s="55"/>
       <c r="I106" s="55"/>
       <c r="J106" s="53"/>
       <c r="K106" s="53"/>
       <c r="L106" s="53" t="s">
-        <v>280</v>
-      </c>
-      <c r="M106" s="56" t="n">
+        <v>274</v>
+      </c>
+      <c r="M106" s="56" t="str">
         <f aca="false">IF(COUNT(G106:I106)=0,"",MIN(G106:I106))</f>
-        <v>190</v>
+        <v/>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8391,7 +8416,7 @@
         <v>11</v>
       </c>
       <c r="C107" s="53" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D107" s="54" t="s">
         <v>281</v>
@@ -8401,7 +8426,7 @@
         <v>282</v>
       </c>
       <c r="G107" s="55" t="n">
-        <f aca="false">IF('Kasa Önü'!D9="","",'Kasa Önü'!D9)</f>
+        <f aca="false">IF('Kasa Önü'!D8="","",'Kasa Önü'!D8)</f>
         <v>190</v>
       </c>
       <c r="H107" s="55"/>
@@ -8409,7 +8434,7 @@
       <c r="J107" s="53"/>
       <c r="K107" s="53"/>
       <c r="L107" s="53" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M107" s="56" t="n">
         <f aca="false">IF(COUNT(G107:I107)=0,"",MIN(G107:I107))</f>
@@ -8421,29 +8446,29 @@
         <v>11</v>
       </c>
       <c r="C108" s="53" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D108" s="54" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E108" s="53"/>
       <c r="F108" s="53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G108" s="55" t="n">
-        <f aca="false">IF('Kasa Önü'!D10="","",'Kasa Önü'!D10)</f>
-        <v>210</v>
+        <f aca="false">IF('Kasa Önü'!D9="","",'Kasa Önü'!D9)</f>
+        <v>190</v>
       </c>
       <c r="H108" s="55"/>
       <c r="I108" s="55"/>
       <c r="J108" s="53"/>
       <c r="K108" s="53"/>
       <c r="L108" s="53" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M108" s="56" t="n">
         <f aca="false">IF(COUNT(G108:I108)=0,"",MIN(G108:I108))</f>
-        <v>210</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8451,17 +8476,17 @@
         <v>11</v>
       </c>
       <c r="C109" s="53" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D109" s="54" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E109" s="53"/>
       <c r="F109" s="53" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G109" s="55" t="n">
-        <f aca="false">IF('Kasa Önü'!D11="","",'Kasa Önü'!D11)</f>
+        <f aca="false">IF('Kasa Önü'!D10="","",'Kasa Önü'!D10)</f>
         <v>210</v>
       </c>
       <c r="H109" s="55"/>
@@ -8469,15 +8494,45 @@
       <c r="J109" s="53"/>
       <c r="K109" s="53"/>
       <c r="L109" s="53" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M109" s="56" t="n">
         <f aca="false">IF(COUNT(G109:I109)=0,"",MIN(G109:I109))</f>
         <v>210</v>
       </c>
     </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" s="53" t="s">
+        <v>280</v>
+      </c>
+      <c r="D110" s="54" t="s">
+        <v>288</v>
+      </c>
+      <c r="E110" s="53"/>
+      <c r="F110" s="53" t="s">
+        <v>289</v>
+      </c>
+      <c r="G110" s="55" t="n">
+        <f aca="false">IF('Kasa Önü'!D11="","",'Kasa Önü'!D11)</f>
+        <v>210</v>
+      </c>
+      <c r="H110" s="55"/>
+      <c r="I110" s="55"/>
+      <c r="J110" s="53"/>
+      <c r="K110" s="53"/>
+      <c r="L110" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="M110" s="56" t="n">
+        <f aca="false">IF(COUNT(G110:I110)=0,"",MIN(G110:I110))</f>
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B5:M109"/>
+  <autoFilter ref="B5:M110"/>
   <mergeCells count="2">
     <mergeCell ref="C1:M2"/>
     <mergeCell ref="B3:M3"/>
@@ -8499,7 +8554,7 @@
     <tabColor rgb="FF2B2320"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:J176"/>
+  <dimension ref="B1:J177"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -8516,7 +8571,7 @@
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -8539,7 +8594,7 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -8552,39 +8607,39 @@
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="57" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D6" s="59" t="s">
         <v>34</v>
@@ -8600,17 +8655,17 @@
         <v>110</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I6" s="60"/>
       <c r="J6" s="58"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D7" s="59" t="s">
         <v>36</v>
@@ -8626,17 +8681,17 @@
         <v>130</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I7" s="60"/>
       <c r="J7" s="58"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D8" s="59" t="s">
         <v>38</v>
@@ -8652,17 +8707,17 @@
         <v>130</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I8" s="60"/>
       <c r="J8" s="58"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D9" s="59" t="s">
         <v>40</v>
@@ -8678,17 +8733,17 @@
         <v>130</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I9" s="60"/>
       <c r="J9" s="58"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D10" s="59" t="s">
         <v>42</v>
@@ -8704,17 +8759,17 @@
         <v>130</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I10" s="60"/>
       <c r="J10" s="58"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D11" s="59" t="s">
         <v>44</v>
@@ -8730,17 +8785,17 @@
         <v>150</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I11" s="60"/>
       <c r="J11" s="58"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D12" s="59" t="s">
         <v>46</v>
@@ -8756,17 +8811,17 @@
         <v>180</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I12" s="60"/>
       <c r="J12" s="58"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D13" s="59" t="s">
         <v>49</v>
@@ -8782,17 +8837,17 @@
         <v>150</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I13" s="60"/>
       <c r="J13" s="58"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D14" s="59" t="s">
         <v>49</v>
@@ -8808,17 +8863,17 @@
         <v>170</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I14" s="60"/>
       <c r="J14" s="58"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D15" s="59" t="s">
         <v>51</v>
@@ -8834,17 +8889,17 @@
         <v>150</v>
       </c>
       <c r="H15" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I15" s="60"/>
       <c r="J15" s="58"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D16" s="59" t="s">
         <v>51</v>
@@ -8860,17 +8915,17 @@
         <v>170</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I16" s="60"/>
       <c r="J16" s="58"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D17" s="59" t="s">
         <v>53</v>
@@ -8886,17 +8941,17 @@
         <v>200</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I17" s="60"/>
       <c r="J17" s="58"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>53</v>
@@ -8912,17 +8967,17 @@
         <v>220</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I18" s="60"/>
       <c r="J18" s="58"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D19" s="59" t="s">
         <v>54</v>
@@ -8938,17 +8993,17 @@
         <v>220</v>
       </c>
       <c r="H19" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I19" s="60"/>
       <c r="J19" s="58"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D20" s="59" t="s">
         <v>54</v>
@@ -8964,17 +9019,17 @@
         <v>240</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I20" s="60"/>
       <c r="J20" s="58"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D21" s="59" t="s">
         <v>56</v>
@@ -8990,17 +9045,17 @@
         <v>210</v>
       </c>
       <c r="H21" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I21" s="60"/>
       <c r="J21" s="58"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D22" s="59" t="s">
         <v>56</v>
@@ -9016,17 +9071,17 @@
         <v>230</v>
       </c>
       <c r="H22" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I22" s="60"/>
       <c r="J22" s="58"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D23" s="59" t="s">
         <v>58</v>
@@ -9042,17 +9097,17 @@
         <v>200</v>
       </c>
       <c r="H23" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I23" s="60"/>
       <c r="J23" s="58"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D24" s="59" t="s">
         <v>58</v>
@@ -9068,17 +9123,17 @@
         <v>220</v>
       </c>
       <c r="H24" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I24" s="60"/>
       <c r="J24" s="58"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D25" s="59" t="s">
         <v>60</v>
@@ -9094,17 +9149,17 @@
         <v>150</v>
       </c>
       <c r="H25" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I25" s="60"/>
       <c r="J25" s="58"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D26" s="59" t="s">
         <v>60</v>
@@ -9120,17 +9175,17 @@
         <v>170</v>
       </c>
       <c r="H26" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I26" s="60"/>
       <c r="J26" s="58"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D27" s="59" t="s">
         <v>63</v>
@@ -9146,17 +9201,17 @@
         <v>230</v>
       </c>
       <c r="H27" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I27" s="60"/>
       <c r="J27" s="58"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C28" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D28" s="59" t="s">
         <v>63</v>
@@ -9172,17 +9227,17 @@
         <v>250</v>
       </c>
       <c r="H28" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I28" s="60"/>
       <c r="J28" s="58"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C29" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D29" s="59" t="s">
         <v>65</v>
@@ -9198,17 +9253,17 @@
         <v>230</v>
       </c>
       <c r="H29" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I29" s="60"/>
       <c r="J29" s="58"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D30" s="59" t="s">
         <v>65</v>
@@ -9224,17 +9279,17 @@
         <v>250</v>
       </c>
       <c r="H30" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I30" s="60"/>
       <c r="J30" s="58"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C31" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D31" s="59" t="s">
         <v>67</v>
@@ -9250,17 +9305,17 @@
         <v>230</v>
       </c>
       <c r="H31" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I31" s="60"/>
       <c r="J31" s="58"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C32" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D32" s="59" t="s">
         <v>67</v>
@@ -9276,17 +9331,17 @@
         <v>250</v>
       </c>
       <c r="H32" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I32" s="60"/>
       <c r="J32" s="58"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D33" s="59" t="s">
         <v>69</v>
@@ -9302,17 +9357,17 @@
         <v>240</v>
       </c>
       <c r="H33" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I33" s="60"/>
       <c r="J33" s="58"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D34" s="59" t="s">
         <v>69</v>
@@ -9328,17 +9383,17 @@
         <v>260</v>
       </c>
       <c r="H34" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I34" s="60"/>
       <c r="J34" s="58"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C35" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D35" s="59" t="s">
         <v>71</v>
@@ -9354,17 +9409,17 @@
         <v>250</v>
       </c>
       <c r="H35" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I35" s="60"/>
       <c r="J35" s="58"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D36" s="59" t="s">
         <v>71</v>
@@ -9380,17 +9435,17 @@
         <v>270</v>
       </c>
       <c r="H36" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I36" s="60"/>
       <c r="J36" s="58"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C37" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D37" s="59" t="s">
         <v>73</v>
@@ -9406,17 +9461,17 @@
         <v>270</v>
       </c>
       <c r="H37" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I37" s="60"/>
       <c r="J37" s="58"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D38" s="59" t="s">
         <v>73</v>
@@ -9432,17 +9487,17 @@
         <v>300</v>
       </c>
       <c r="H38" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I38" s="60"/>
       <c r="J38" s="58"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C39" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D39" s="59" t="s">
         <v>75</v>
@@ -9458,17 +9513,17 @@
         <v>300</v>
       </c>
       <c r="H39" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I39" s="60"/>
       <c r="J39" s="58"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D40" s="59" t="s">
         <v>75</v>
@@ -9484,17 +9539,17 @@
         <v>340</v>
       </c>
       <c r="H40" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I40" s="60"/>
       <c r="J40" s="58"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C41" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D41" s="59" t="s">
         <v>78</v>
@@ -9510,17 +9565,17 @@
         <v>250</v>
       </c>
       <c r="H41" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I41" s="60"/>
       <c r="J41" s="58"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C42" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D42" s="59" t="s">
         <v>78</v>
@@ -9536,17 +9591,17 @@
         <v>270</v>
       </c>
       <c r="H42" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I42" s="60"/>
       <c r="J42" s="58"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C43" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D43" s="59" t="s">
         <v>80</v>
@@ -9562,17 +9617,17 @@
         <v>250</v>
       </c>
       <c r="H43" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I43" s="60"/>
       <c r="J43" s="58"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C44" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D44" s="59" t="s">
         <v>80</v>
@@ -9588,17 +9643,17 @@
         <v>270</v>
       </c>
       <c r="H44" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I44" s="60"/>
       <c r="J44" s="58"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C45" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D45" s="59" t="s">
         <v>82</v>
@@ -9614,17 +9669,17 @@
         <v>230</v>
       </c>
       <c r="H45" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I45" s="60"/>
       <c r="J45" s="58"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C46" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D46" s="59" t="s">
         <v>82</v>
@@ -9640,17 +9695,17 @@
         <v>250</v>
       </c>
       <c r="H46" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I46" s="60"/>
       <c r="J46" s="58"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C47" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D47" s="59" t="s">
         <v>84</v>
@@ -9666,17 +9721,17 @@
         <v>230</v>
       </c>
       <c r="H47" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I47" s="60"/>
       <c r="J47" s="58"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C48" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D48" s="59" t="s">
         <v>84</v>
@@ -9692,17 +9747,17 @@
         <v>250</v>
       </c>
       <c r="H48" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I48" s="60"/>
       <c r="J48" s="58"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C49" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D49" s="59" t="s">
         <v>86</v>
@@ -9718,17 +9773,17 @@
         <v>260</v>
       </c>
       <c r="H49" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I49" s="60"/>
       <c r="J49" s="58"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C50" s="58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D50" s="59" t="s">
         <v>86</v>
@@ -9744,14 +9799,14 @@
         <v>280</v>
       </c>
       <c r="H50" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I50" s="60"/>
       <c r="J50" s="58"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C51" s="58" t="s">
         <v>89</v>
@@ -9770,14 +9825,14 @@
         <v>145</v>
       </c>
       <c r="H51" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I51" s="60"/>
       <c r="J51" s="58"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C52" s="58" t="s">
         <v>89</v>
@@ -9796,14 +9851,14 @@
         <v>160</v>
       </c>
       <c r="H52" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I52" s="60"/>
       <c r="J52" s="58"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C53" s="58" t="s">
         <v>89</v>
@@ -9822,14 +9877,14 @@
         <v>150</v>
       </c>
       <c r="H53" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I53" s="60"/>
       <c r="J53" s="58"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C54" s="58" t="s">
         <v>89</v>
@@ -9848,17 +9903,17 @@
         <v>165</v>
       </c>
       <c r="H54" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I54" s="60"/>
       <c r="J54" s="58"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C55" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D55" s="59" t="s">
         <v>98</v>
@@ -9872,17 +9927,17 @@
         <v>70</v>
       </c>
       <c r="H55" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I55" s="60"/>
       <c r="J55" s="58"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C56" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D56" s="59" t="s">
         <v>99</v>
@@ -9896,17 +9951,17 @@
         <v>90</v>
       </c>
       <c r="H56" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I56" s="60"/>
       <c r="J56" s="58"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C57" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D57" s="59" t="s">
         <v>100</v>
@@ -9922,7 +9977,7 @@
         <v>100</v>
       </c>
       <c r="H57" s="58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I57" s="60"/>
       <c r="J57" s="58" t="s">
@@ -9931,10 +9986,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C58" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D58" s="59" t="s">
         <v>100</v>
@@ -9950,7 +10005,7 @@
         <v>110</v>
       </c>
       <c r="H58" s="58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I58" s="60"/>
       <c r="J58" s="58" t="s">
@@ -9959,10 +10014,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C59" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D59" s="59" t="s">
         <v>103</v>
@@ -9978,17 +10033,17 @@
         <v>130</v>
       </c>
       <c r="H59" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I59" s="60"/>
       <c r="J59" s="58"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C60" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D60" s="59" t="s">
         <v>105</v>
@@ -10004,17 +10059,17 @@
         <v>130</v>
       </c>
       <c r="H60" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I60" s="60"/>
       <c r="J60" s="58"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C61" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D61" s="59" t="s">
         <v>107</v>
@@ -10030,17 +10085,17 @@
         <v>130</v>
       </c>
       <c r="H61" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I61" s="60"/>
       <c r="J61" s="58"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C62" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D62" s="59" t="s">
         <v>109</v>
@@ -10056,17 +10111,17 @@
         <v>130</v>
       </c>
       <c r="H62" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I62" s="60"/>
       <c r="J62" s="58"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C63" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D63" s="59" t="s">
         <v>111</v>
@@ -10082,17 +10137,17 @@
         <v>130</v>
       </c>
       <c r="H63" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I63" s="60"/>
       <c r="J63" s="58"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D64" s="59" t="s">
         <v>113</v>
@@ -10108,17 +10163,17 @@
         <v>130</v>
       </c>
       <c r="H64" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I64" s="60"/>
       <c r="J64" s="58"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C65" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D65" s="59" t="s">
         <v>116</v>
@@ -10134,17 +10189,17 @@
         <v>290</v>
       </c>
       <c r="H65" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I65" s="60"/>
       <c r="J65" s="58"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D66" s="59" t="s">
         <v>116</v>
@@ -10160,17 +10215,17 @@
         <v>320</v>
       </c>
       <c r="H66" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I66" s="60"/>
       <c r="J66" s="58"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C67" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D67" s="59" t="s">
         <v>119</v>
@@ -10186,17 +10241,17 @@
         <v>300</v>
       </c>
       <c r="H67" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I67" s="60"/>
       <c r="J67" s="58"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C68" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D68" s="59" t="s">
         <v>119</v>
@@ -10212,17 +10267,17 @@
         <v>340</v>
       </c>
       <c r="H68" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I68" s="60"/>
       <c r="J68" s="58"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C69" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D69" s="59" t="s">
         <v>121</v>
@@ -10238,17 +10293,17 @@
         <v>290</v>
       </c>
       <c r="H69" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I69" s="60"/>
       <c r="J69" s="58"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C70" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D70" s="59" t="s">
         <v>121</v>
@@ -10264,17 +10319,17 @@
         <v>320</v>
       </c>
       <c r="H70" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I70" s="60"/>
       <c r="J70" s="58"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C71" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D71" s="59" t="s">
         <v>123</v>
@@ -10290,17 +10345,17 @@
         <v>275</v>
       </c>
       <c r="H71" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I71" s="60"/>
       <c r="J71" s="58"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C72" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D72" s="59" t="s">
         <v>123</v>
@@ -10316,17 +10371,17 @@
         <v>305</v>
       </c>
       <c r="H72" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I72" s="60"/>
       <c r="J72" s="58"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C73" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D73" s="59" t="s">
         <v>125</v>
@@ -10342,17 +10397,17 @@
         <v>290</v>
       </c>
       <c r="H73" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I73" s="60"/>
       <c r="J73" s="58"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="61" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C74" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D74" s="59" t="s">
         <v>125</v>
@@ -10368,17 +10423,17 @@
         <v>320</v>
       </c>
       <c r="H74" s="58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I74" s="60"/>
       <c r="J74" s="58"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="57" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C75" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D75" s="59" t="s">
         <v>137</v>
@@ -10394,17 +10449,17 @@
         <v>170</v>
       </c>
       <c r="H75" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I75" s="60"/>
       <c r="J75" s="58"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C76" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D76" s="59" t="s">
         <v>137</v>
@@ -10420,17 +10475,17 @@
         <v>190</v>
       </c>
       <c r="H76" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I76" s="60"/>
       <c r="J76" s="58"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C77" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D77" s="59" t="s">
         <v>139</v>
@@ -10446,17 +10501,17 @@
         <v>220</v>
       </c>
       <c r="H77" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I77" s="60"/>
       <c r="J77" s="58"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C78" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D78" s="59" t="s">
         <v>139</v>
@@ -10472,17 +10527,17 @@
         <v>240</v>
       </c>
       <c r="H78" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I78" s="60"/>
       <c r="J78" s="58"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C79" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D79" s="59" t="s">
         <v>141</v>
@@ -10498,17 +10553,17 @@
         <v>240</v>
       </c>
       <c r="H79" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I79" s="60"/>
       <c r="J79" s="58"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C80" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D80" s="59" t="s">
         <v>141</v>
@@ -10524,17 +10579,17 @@
         <v>260</v>
       </c>
       <c r="H80" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I80" s="60"/>
       <c r="J80" s="58"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C81" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D81" s="59" t="s">
         <v>143</v>
@@ -10550,17 +10605,17 @@
         <v>230</v>
       </c>
       <c r="H81" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I81" s="60"/>
       <c r="J81" s="58"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C82" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D82" s="59" t="s">
         <v>143</v>
@@ -10576,17 +10631,17 @@
         <v>250</v>
       </c>
       <c r="H82" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I82" s="60"/>
       <c r="J82" s="58"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C83" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D83" s="59" t="s">
         <v>145</v>
@@ -10602,17 +10657,17 @@
         <v>250</v>
       </c>
       <c r="H83" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I83" s="60"/>
       <c r="J83" s="58"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C84" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D84" s="59" t="s">
         <v>145</v>
@@ -10628,17 +10683,17 @@
         <v>280</v>
       </c>
       <c r="H84" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I84" s="60"/>
       <c r="J84" s="58"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C85" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D85" s="59" t="s">
         <v>147</v>
@@ -10654,17 +10709,17 @@
         <v>150</v>
       </c>
       <c r="H85" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I85" s="60"/>
       <c r="J85" s="58"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C86" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D86" s="59" t="s">
         <v>147</v>
@@ -10680,17 +10735,17 @@
         <v>170</v>
       </c>
       <c r="H86" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I86" s="60"/>
       <c r="J86" s="58"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C87" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D87" s="59" t="s">
         <v>149</v>
@@ -10706,17 +10761,17 @@
         <v>250</v>
       </c>
       <c r="H87" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I87" s="60"/>
       <c r="J87" s="58"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C88" s="58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D88" s="59" t="s">
         <v>149</v>
@@ -10732,17 +10787,17 @@
         <v>270</v>
       </c>
       <c r="H88" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I88" s="60"/>
       <c r="J88" s="58"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C89" s="58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D89" s="59" t="s">
         <v>152</v>
@@ -10758,17 +10813,17 @@
         <v>150</v>
       </c>
       <c r="H89" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I89" s="60"/>
       <c r="J89" s="58"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C90" s="58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D90" s="59" t="s">
         <v>152</v>
@@ -10784,17 +10839,17 @@
         <v>170</v>
       </c>
       <c r="H90" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I90" s="60"/>
       <c r="J90" s="58"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C91" s="58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D91" s="59" t="s">
         <v>154</v>
@@ -10810,17 +10865,17 @@
         <v>170</v>
       </c>
       <c r="H91" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I91" s="60"/>
       <c r="J91" s="58"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C92" s="58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D92" s="59" t="s">
         <v>154</v>
@@ -10836,14 +10891,14 @@
         <v>190</v>
       </c>
       <c r="H92" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I92" s="60"/>
       <c r="J92" s="58"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C93" s="58" t="s">
         <v>157</v>
@@ -10862,14 +10917,14 @@
         <v>170</v>
       </c>
       <c r="H93" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I93" s="60"/>
       <c r="J93" s="58"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C94" s="58" t="s">
         <v>157</v>
@@ -10888,17 +10943,17 @@
         <v>190</v>
       </c>
       <c r="H94" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I94" s="60"/>
       <c r="J94" s="58"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C95" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D95" s="59" t="s">
         <v>160</v>
@@ -10914,17 +10969,17 @@
         <v>250</v>
       </c>
       <c r="H95" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I95" s="60"/>
       <c r="J95" s="58"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C96" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D96" s="59" t="s">
         <v>160</v>
@@ -10940,17 +10995,17 @@
         <v>270</v>
       </c>
       <c r="H96" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I96" s="60"/>
       <c r="J96" s="58"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C97" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D97" s="59" t="s">
         <v>161</v>
@@ -10966,17 +11021,17 @@
         <v>250</v>
       </c>
       <c r="H97" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I97" s="60"/>
       <c r="J97" s="58"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C98" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D98" s="59" t="s">
         <v>161</v>
@@ -10992,17 +11047,17 @@
         <v>270</v>
       </c>
       <c r="H98" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I98" s="60"/>
       <c r="J98" s="58"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C99" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D99" s="59" t="s">
         <v>163</v>
@@ -11018,17 +11073,17 @@
         <v>250</v>
       </c>
       <c r="H99" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I99" s="60"/>
       <c r="J99" s="58"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C100" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D100" s="59" t="s">
         <v>163</v>
@@ -11044,17 +11099,17 @@
         <v>270</v>
       </c>
       <c r="H100" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I100" s="60"/>
       <c r="J100" s="58"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C101" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D101" s="59" t="s">
         <v>165</v>
@@ -11070,17 +11125,17 @@
         <v>240</v>
       </c>
       <c r="H101" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I101" s="60"/>
       <c r="J101" s="58"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C102" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D102" s="59" t="s">
         <v>165</v>
@@ -11096,17 +11151,17 @@
         <v>260</v>
       </c>
       <c r="H102" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I102" s="60"/>
       <c r="J102" s="58"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C103" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D103" s="59" t="s">
         <v>167</v>
@@ -11122,17 +11177,17 @@
         <v>260</v>
       </c>
       <c r="H103" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I103" s="60"/>
       <c r="J103" s="58"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C104" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D104" s="59" t="s">
         <v>167</v>
@@ -11148,17 +11203,17 @@
         <v>280</v>
       </c>
       <c r="H104" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I104" s="60"/>
       <c r="J104" s="58"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C105" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D105" s="59" t="s">
         <v>169</v>
@@ -11174,17 +11229,17 @@
         <v>300</v>
       </c>
       <c r="H105" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I105" s="60"/>
       <c r="J105" s="58"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C106" s="58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D106" s="59" t="s">
         <v>169</v>
@@ -11200,17 +11255,17 @@
         <v>340</v>
       </c>
       <c r="H106" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I106" s="60"/>
       <c r="J106" s="58"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C107" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D107" s="59" t="s">
         <v>172</v>
@@ -11226,17 +11281,17 @@
         <v>280</v>
       </c>
       <c r="H107" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I107" s="60"/>
       <c r="J107" s="58"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C108" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D108" s="59" t="s">
         <v>172</v>
@@ -11252,17 +11307,17 @@
         <v>300</v>
       </c>
       <c r="H108" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I108" s="60"/>
       <c r="J108" s="58"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C109" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D109" s="59" t="s">
         <v>174</v>
@@ -11278,17 +11333,17 @@
         <v>270</v>
       </c>
       <c r="H109" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I109" s="60"/>
       <c r="J109" s="58"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C110" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D110" s="59" t="s">
         <v>174</v>
@@ -11304,17 +11359,17 @@
         <v>290</v>
       </c>
       <c r="H110" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I110" s="60"/>
       <c r="J110" s="58"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C111" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D111" s="59" t="s">
         <v>176</v>
@@ -11330,17 +11385,17 @@
         <v>270</v>
       </c>
       <c r="H111" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I111" s="60"/>
       <c r="J111" s="58"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C112" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D112" s="59" t="s">
         <v>176</v>
@@ -11356,17 +11411,17 @@
         <v>290</v>
       </c>
       <c r="H112" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I112" s="60"/>
       <c r="J112" s="58"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C113" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D113" s="59" t="s">
         <v>178</v>
@@ -11382,17 +11437,17 @@
         <v>300</v>
       </c>
       <c r="H113" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I113" s="60"/>
       <c r="J113" s="58"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C114" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D114" s="59" t="s">
         <v>178</v>
@@ -11408,17 +11463,17 @@
         <v>320</v>
       </c>
       <c r="H114" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I114" s="60"/>
       <c r="J114" s="58"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C115" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D115" s="59" t="s">
         <v>180</v>
@@ -11434,17 +11489,17 @@
         <v>300</v>
       </c>
       <c r="H115" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I115" s="60"/>
       <c r="J115" s="58"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C116" s="58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D116" s="59" t="s">
         <v>180</v>
@@ -11460,17 +11515,17 @@
         <v>320</v>
       </c>
       <c r="H116" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I116" s="60"/>
       <c r="J116" s="58"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C117" s="58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D117" s="59" t="s">
         <v>183</v>
@@ -11486,17 +11541,17 @@
         <v>260</v>
       </c>
       <c r="H117" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I117" s="60"/>
       <c r="J117" s="58"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C118" s="58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D118" s="59" t="s">
         <v>183</v>
@@ -11512,17 +11567,17 @@
         <v>280</v>
       </c>
       <c r="H118" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I118" s="60"/>
       <c r="J118" s="58"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C119" s="58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D119" s="59" t="s">
         <v>185</v>
@@ -11538,17 +11593,17 @@
         <v>260</v>
       </c>
       <c r="H119" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I119" s="60"/>
       <c r="J119" s="58"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C120" s="58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D120" s="59" t="s">
         <v>185</v>
@@ -11564,17 +11619,17 @@
         <v>280</v>
       </c>
       <c r="H120" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I120" s="60"/>
       <c r="J120" s="58"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C121" s="58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D121" s="59" t="s">
         <v>186</v>
@@ -11590,17 +11645,17 @@
         <v>240</v>
       </c>
       <c r="H121" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I121" s="60"/>
       <c r="J121" s="58"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C122" s="58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D122" s="59" t="s">
         <v>186</v>
@@ -11616,17 +11671,17 @@
         <v>260</v>
       </c>
       <c r="H122" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I122" s="60"/>
       <c r="J122" s="58"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C123" s="58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D123" s="59" t="s">
         <v>188</v>
@@ -11642,17 +11697,17 @@
         <v>270</v>
       </c>
       <c r="H123" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I123" s="60"/>
       <c r="J123" s="58"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C124" s="58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D124" s="59" t="s">
         <v>188</v>
@@ -11668,17 +11723,17 @@
         <v>290</v>
       </c>
       <c r="H124" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I124" s="60"/>
       <c r="J124" s="58"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C125" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D125" s="59" t="s">
         <v>191</v>
@@ -11694,17 +11749,17 @@
         <v>300</v>
       </c>
       <c r="H125" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I125" s="60"/>
       <c r="J125" s="58"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C126" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D126" s="59" t="s">
         <v>191</v>
@@ -11720,17 +11775,17 @@
         <v>320</v>
       </c>
       <c r="H126" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I126" s="60"/>
       <c r="J126" s="58"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C127" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D127" s="59" t="s">
         <v>193</v>
@@ -11746,17 +11801,17 @@
         <v>330</v>
       </c>
       <c r="H127" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I127" s="60"/>
       <c r="J127" s="58"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C128" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D128" s="59" t="s">
         <v>193</v>
@@ -11772,17 +11827,17 @@
         <v>350</v>
       </c>
       <c r="H128" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I128" s="60"/>
       <c r="J128" s="58"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C129" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D129" s="59" t="s">
         <v>195</v>
@@ -11798,17 +11853,17 @@
         <v>290</v>
       </c>
       <c r="H129" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I129" s="60"/>
       <c r="J129" s="58"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C130" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D130" s="59" t="s">
         <v>195</v>
@@ -11824,17 +11879,17 @@
         <v>310</v>
       </c>
       <c r="H130" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I130" s="60"/>
       <c r="J130" s="58"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C131" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D131" s="59" t="s">
         <v>197</v>
@@ -11850,17 +11905,17 @@
         <v>290</v>
       </c>
       <c r="H131" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I131" s="60"/>
       <c r="J131" s="58"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C132" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D132" s="59" t="s">
         <v>197</v>
@@ -11876,17 +11931,17 @@
         <v>310</v>
       </c>
       <c r="H132" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I132" s="60"/>
       <c r="J132" s="58"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C133" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D133" s="59" t="s">
         <v>199</v>
@@ -11902,17 +11957,17 @@
         <v>290</v>
       </c>
       <c r="H133" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I133" s="60"/>
       <c r="J133" s="58"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C134" s="58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D134" s="59" t="s">
         <v>199</v>
@@ -11928,17 +11983,17 @@
         <v>310</v>
       </c>
       <c r="H134" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I134" s="60"/>
       <c r="J134" s="58"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C135" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D135" s="59" t="s">
         <v>116</v>
@@ -11954,17 +12009,17 @@
         <v>300</v>
       </c>
       <c r="H135" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I135" s="60"/>
       <c r="J135" s="58"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C136" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D136" s="59" t="s">
         <v>116</v>
@@ -11980,17 +12035,17 @@
         <v>320</v>
       </c>
       <c r="H136" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I136" s="60"/>
       <c r="J136" s="58"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C137" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D137" s="59" t="s">
         <v>202</v>
@@ -12006,19 +12061,19 @@
         <v>280</v>
       </c>
       <c r="H137" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I137" s="60"/>
       <c r="J137" s="58" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C138" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D138" s="59" t="s">
         <v>202</v>
@@ -12034,19 +12089,19 @@
         <v>300</v>
       </c>
       <c r="H138" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I138" s="60"/>
       <c r="J138" s="58" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C139" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D139" s="59" t="s">
         <v>205</v>
@@ -12062,17 +12117,17 @@
         <v>180</v>
       </c>
       <c r="H139" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I139" s="60"/>
       <c r="J139" s="58"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C140" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D140" s="59" t="s">
         <v>205</v>
@@ -12088,17 +12143,17 @@
         <v>200</v>
       </c>
       <c r="H140" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I140" s="60"/>
       <c r="J140" s="58"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C141" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D141" s="59" t="s">
         <v>207</v>
@@ -12114,17 +12169,17 @@
         <v>180</v>
       </c>
       <c r="H141" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I141" s="60"/>
       <c r="J141" s="58"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C142" s="58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D142" s="59" t="s">
         <v>207</v>
@@ -12140,171 +12195,173 @@
         <v>200</v>
       </c>
       <c r="H142" s="58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I142" s="60"/>
       <c r="J142" s="58"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="57" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C143" s="58" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D143" s="59" t="s">
         <v>210</v>
       </c>
       <c r="E143" s="58"/>
       <c r="F143" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G143" s="55" t="n">
         <f aca="false">IF(Soğuklar!D58="","",Soğuklar!D58)</f>
         <v>40</v>
       </c>
       <c r="H143" s="58" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I143" s="60" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J143" s="58"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="61" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C144" s="58" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D144" s="59" t="s">
         <v>211</v>
       </c>
       <c r="E144" s="58"/>
       <c r="F144" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G144" s="55" t="n">
         <f aca="false">IF(Soğuklar!D59="","",Soğuklar!D59)</f>
         <v>60</v>
       </c>
       <c r="H144" s="58" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I144" s="60" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J144" s="58"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="61" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C145" s="58" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D145" s="59" t="s">
         <v>212</v>
       </c>
       <c r="E145" s="58"/>
       <c r="F145" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G145" s="55" t="n">
         <f aca="false">IF(Soğuklar!D60="","",Soğuklar!D60)</f>
         <v>80</v>
       </c>
       <c r="H145" s="58" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I145" s="60" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J145" s="58"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="61" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C146" s="58" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D146" s="59" t="s">
         <v>213</v>
       </c>
       <c r="E146" s="58"/>
       <c r="F146" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G146" s="55" t="n">
         <f aca="false">IF(Soğuklar!D61="","",Soğuklar!D61)</f>
         <v>120</v>
       </c>
       <c r="H146" s="58" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I146" s="60" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J146" s="58"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="61" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C147" s="58" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D147" s="59" t="s">
         <v>214</v>
       </c>
       <c r="E147" s="58"/>
       <c r="F147" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G147" s="55" t="n">
         <f aca="false">IF(Soğuklar!D62="","",Soğuklar!D62)</f>
         <v>200</v>
       </c>
       <c r="H147" s="58" t="s">
-        <v>325</v>
-      </c>
-      <c r="I147" s="60"/>
+        <v>328</v>
+      </c>
+      <c r="I147" s="60" t="s">
+        <v>337</v>
+      </c>
       <c r="J147" s="58"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="61" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C148" s="58" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D148" s="59" t="s">
         <v>215</v>
       </c>
       <c r="E148" s="58"/>
       <c r="F148" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G148" s="55" t="n">
         <f aca="false">IF(Soğuklar!D63="","",Soğuklar!D63)</f>
         <v>170</v>
       </c>
       <c r="H148" s="58" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I148" s="60" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J148" s="58"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="57" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C149" s="58" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D149" s="59" t="s">
         <v>225</v>
@@ -12313,26 +12370,26 @@
         <v>226</v>
       </c>
       <c r="F149" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G149" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E8="","",'Tatlı &amp; Atıştırmalık'!E8)</f>
         <v>270</v>
       </c>
       <c r="H149" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I149" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I149" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J149" s="58"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B150" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C150" s="58" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D150" s="59" t="s">
         <v>228</v>
@@ -12341,26 +12398,26 @@
         <v>229</v>
       </c>
       <c r="F150" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G150" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E9="","",'Tatlı &amp; Atıştırmalık'!E9)</f>
         <v>270</v>
       </c>
       <c r="H150" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I150" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I150" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J150" s="58"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C151" s="58" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D151" s="59" t="s">
         <v>231</v>
@@ -12369,26 +12426,26 @@
         <v>232</v>
       </c>
       <c r="F151" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G151" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E10="","",'Tatlı &amp; Atıştırmalık'!E10)</f>
         <v>300</v>
       </c>
       <c r="H151" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I151" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I151" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J151" s="58"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C152" s="58" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D152" s="59" t="s">
         <v>234</v>
@@ -12397,26 +12454,26 @@
         <v>235</v>
       </c>
       <c r="F152" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G152" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E11="","",'Tatlı &amp; Atıştırmalık'!E11)</f>
         <v>270</v>
       </c>
       <c r="H152" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I152" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I152" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J152" s="58"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B153" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C153" s="58" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D153" s="59" t="s">
         <v>237</v>
@@ -12425,26 +12482,26 @@
         <v>238</v>
       </c>
       <c r="F153" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G153" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E12="","",'Tatlı &amp; Atıştırmalık'!E12)</f>
         <v>320</v>
       </c>
       <c r="H153" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I153" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I153" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J153" s="58"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C154" s="58" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D154" s="59" t="s">
         <v>240</v>
@@ -12453,26 +12510,26 @@
         <v>241</v>
       </c>
       <c r="F154" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G154" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E13="","",'Tatlı &amp; Atıştırmalık'!E13)</f>
         <v>240</v>
       </c>
       <c r="H154" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I154" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I154" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J154" s="58"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C155" s="58" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D155" s="59" t="s">
         <v>243</v>
@@ -12481,26 +12538,26 @@
         <v>244</v>
       </c>
       <c r="F155" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G155" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E14="","",'Tatlı &amp; Atıştırmalık'!E14)</f>
         <v>250</v>
       </c>
       <c r="H155" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I155" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I155" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J155" s="58"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C156" s="58" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D156" s="59" t="s">
         <v>246</v>
@@ -12509,26 +12566,26 @@
         <v>247</v>
       </c>
       <c r="F156" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G156" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E15="","",'Tatlı &amp; Atıştırmalık'!E15)</f>
         <v>250</v>
       </c>
       <c r="H156" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I156" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I156" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J156" s="58"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B157" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C157" s="58" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D157" s="59" t="s">
         <v>250</v>
@@ -12537,26 +12594,26 @@
         <v>251</v>
       </c>
       <c r="F157" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G157" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E18="","",'Tatlı &amp; Atıştırmalık'!E18)</f>
         <v>300</v>
       </c>
       <c r="H157" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I157" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I157" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J157" s="58"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C158" s="58" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D158" s="59" t="s">
         <v>253</v>
@@ -12565,26 +12622,26 @@
         <v>254</v>
       </c>
       <c r="F158" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G158" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E19="","",'Tatlı &amp; Atıştırmalık'!E19)</f>
         <v>200</v>
       </c>
       <c r="H158" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I158" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I158" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J158" s="58"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C159" s="58" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D159" s="59" t="s">
         <v>256</v>
@@ -12593,26 +12650,26 @@
         <v>257</v>
       </c>
       <c r="F159" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G159" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E20="","",'Tatlı &amp; Atıştırmalık'!E20)</f>
         <v>270</v>
       </c>
       <c r="H159" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I159" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I159" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J159" s="58"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B160" s="61" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C160" s="58" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D160" s="59" t="s">
         <v>259</v>
@@ -12621,82 +12678,82 @@
         <v>260</v>
       </c>
       <c r="F160" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G160" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E21="","",'Tatlı &amp; Atıştırmalık'!E21)</f>
+        <v>200</v>
+      </c>
+      <c r="H160" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I160" s="60" t="s">
+        <v>337</v>
+      </c>
+      <c r="J160" s="58"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B161" s="61" t="s">
+        <v>338</v>
+      </c>
+      <c r="C161" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="D161" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="E161" s="58" t="s">
+        <v>263</v>
+      </c>
+      <c r="F161" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G161" s="55" t="n">
+        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E22="","",'Tatlı &amp; Atıştırmalık'!E22)</f>
         <v>170</v>
       </c>
-      <c r="H160" s="58" t="s">
+      <c r="H161" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I161" s="60" t="s">
         <v>337</v>
       </c>
-      <c r="I160" s="60" t="s">
-        <v>334</v>
-      </c>
-      <c r="J160" s="58"/>
-    </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="C161" s="58" t="s">
-        <v>339</v>
-      </c>
-      <c r="D161" s="59" t="s">
-        <v>263</v>
-      </c>
-      <c r="E161" s="58" t="s">
-        <v>264</v>
-      </c>
-      <c r="F161" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G161" s="55" t="n">
-        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E24="","",'Tatlı &amp; Atıştırmalık'!E24)</f>
-        <v>200</v>
-      </c>
-      <c r="H161" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="I161" s="60" t="s">
-        <v>334</v>
-      </c>
       <c r="J161" s="58"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="61" t="s">
-        <v>338</v>
+      <c r="B162" s="57" t="s">
+        <v>341</v>
       </c>
       <c r="C162" s="58" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D162" s="59" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E162" s="58" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F162" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G162" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E25="","",'Tatlı &amp; Atıştırmalık'!E25)</f>
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H162" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I162" s="60" t="s">
         <v>337</v>
-      </c>
-      <c r="I162" s="60" t="s">
-        <v>334</v>
       </c>
       <c r="J162" s="58"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="61" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C163" s="58" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D163" s="59" t="s">
         <v>268</v>
@@ -12705,106 +12762,104 @@
         <v>269</v>
       </c>
       <c r="F163" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G163" s="55" t="str">
-        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E28="","",'Tatlı &amp; Atıştırmalık'!E28)</f>
-        <v/>
+        <v>335</v>
+      </c>
+      <c r="G163" s="55" t="n">
+        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E26="","",'Tatlı &amp; Atıştırmalık'!E26)</f>
+        <v>250</v>
       </c>
       <c r="H163" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I163" s="60" t="s">
         <v>337</v>
       </c>
-      <c r="I163" s="60"/>
-      <c r="J163" s="58" t="s">
-        <v>271</v>
-      </c>
+      <c r="J163" s="58"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="61" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C164" s="58" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D164" s="59" t="s">
+        <v>271</v>
+      </c>
+      <c r="E164" s="58" t="s">
         <v>272</v>
       </c>
-      <c r="E164" s="58" t="s">
-        <v>273</v>
-      </c>
       <c r="F164" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G164" s="55" t="str">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E29="","",'Tatlı &amp; Atıştırmalık'!E29)</f>
         <v/>
       </c>
       <c r="H164" s="58" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I164" s="60"/>
       <c r="J164" s="58" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="57" t="s">
+      <c r="B165" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="C165" s="58" t="s">
+        <v>343</v>
+      </c>
+      <c r="D165" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="E165" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F165" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G165" s="55" t="str">
+        <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E30="","",'Tatlı &amp; Atıştırmalık'!E30)</f>
+        <v/>
+      </c>
+      <c r="H165" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I165" s="60"/>
+      <c r="J165" s="58" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B166" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="C165" s="58" t="s">
-        <v>341</v>
-      </c>
-      <c r="D165" s="59" t="s">
-        <v>278</v>
-      </c>
-      <c r="E165" s="58" t="s">
-        <v>279</v>
-      </c>
-      <c r="F165" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G165" s="55" t="n">
+      <c r="C166" s="58" t="s">
+        <v>344</v>
+      </c>
+      <c r="D166" s="59" t="s">
+        <v>281</v>
+      </c>
+      <c r="E166" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="F166" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G166" s="55" t="n">
         <f aca="false">IF('Kasa Önü'!D8="","",'Kasa Önü'!D8)</f>
         <v>190</v>
       </c>
-      <c r="H165" s="58" t="s">
-        <v>342</v>
-      </c>
-      <c r="I165" s="60" t="s">
-        <v>334</v>
-      </c>
-      <c r="J165" s="58" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="C166" s="58" t="s">
-        <v>341</v>
-      </c>
-      <c r="D166" s="59" t="s">
-        <v>281</v>
-      </c>
-      <c r="E166" s="58" t="s">
-        <v>282</v>
-      </c>
-      <c r="F166" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G166" s="55" t="n">
-        <f aca="false">IF('Kasa Önü'!D9="","",'Kasa Önü'!D9)</f>
-        <v>190</v>
-      </c>
       <c r="H166" s="58" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I166" s="60" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J166" s="58" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12812,29 +12867,29 @@
         <v>11</v>
       </c>
       <c r="C167" s="58" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D167" s="59" t="s">
+        <v>284</v>
+      </c>
+      <c r="E167" s="58" t="s">
+        <v>285</v>
+      </c>
+      <c r="F167" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G167" s="55" t="n">
+        <f aca="false">IF('Kasa Önü'!D9="","",'Kasa Önü'!D9)</f>
+        <v>190</v>
+      </c>
+      <c r="H167" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="I167" s="60" t="s">
+        <v>337</v>
+      </c>
+      <c r="J167" s="58" t="s">
         <v>283</v>
-      </c>
-      <c r="E167" s="58" t="s">
-        <v>284</v>
-      </c>
-      <c r="F167" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G167" s="55" t="n">
-        <f aca="false">IF('Kasa Önü'!D10="","",'Kasa Önü'!D10)</f>
-        <v>210</v>
-      </c>
-      <c r="H167" s="58" t="s">
-        <v>342</v>
-      </c>
-      <c r="I167" s="60" t="s">
-        <v>334</v>
-      </c>
-      <c r="J167" s="58" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12842,241 +12897,271 @@
         <v>11</v>
       </c>
       <c r="C168" s="58" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D168" s="59" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E168" s="58" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F168" s="60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G168" s="55" t="n">
+        <f aca="false">IF('Kasa Önü'!D10="","",'Kasa Önü'!D10)</f>
+        <v>210</v>
+      </c>
+      <c r="H168" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="I168" s="60" t="s">
+        <v>337</v>
+      </c>
+      <c r="J168" s="58" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B169" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="58" t="s">
+        <v>344</v>
+      </c>
+      <c r="D169" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="E169" s="58" t="s">
+        <v>289</v>
+      </c>
+      <c r="F169" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G169" s="55" t="n">
         <f aca="false">IF('Kasa Önü'!D11="","",'Kasa Önü'!D11)</f>
         <v>210</v>
       </c>
-      <c r="H168" s="58" t="s">
-        <v>342</v>
-      </c>
-      <c r="I168" s="60" t="s">
-        <v>334</v>
-      </c>
-      <c r="J168" s="58" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="C169" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="D169" s="59" t="s">
+      <c r="H169" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="I169" s="60" t="s">
+        <v>337</v>
+      </c>
+      <c r="J169" s="58" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B170" s="57" t="s">
+        <v>346</v>
+      </c>
+      <c r="C170" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D170" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E169" s="58"/>
-      <c r="F169" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G169" s="55" t="n">
+      <c r="E170" s="58"/>
+      <c r="F170" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G170" s="55" t="n">
         <f aca="false">Sıcaklar!D66</f>
         <v>45</v>
       </c>
-      <c r="H169" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="I169" s="60"/>
-      <c r="J169" s="58" t="s">
+      <c r="H170" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="I170" s="60"/>
+      <c r="J170" s="58" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B171" s="61" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="61" t="s">
-        <v>343</v>
-      </c>
-      <c r="C170" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="D170" s="59" t="s">
+      <c r="C171" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D171" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E170" s="58"/>
-      <c r="F170" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G170" s="55" t="n">
+      <c r="E171" s="58"/>
+      <c r="F171" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G171" s="55" t="n">
         <f aca="false">Sıcaklar!D67</f>
         <v>60</v>
       </c>
-      <c r="H170" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="I170" s="60"/>
-      <c r="J170" s="58" t="s">
+      <c r="H171" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="I171" s="60"/>
+      <c r="J171" s="58" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B172" s="61" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="61" t="s">
-        <v>343</v>
-      </c>
-      <c r="C171" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="D171" s="59" t="s">
+      <c r="C172" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D172" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="E171" s="58"/>
-      <c r="F171" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G171" s="55" t="n">
+      <c r="E172" s="58"/>
+      <c r="F172" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G172" s="55" t="n">
         <f aca="false">Sıcaklar!D68</f>
         <v>60</v>
       </c>
-      <c r="H171" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="I171" s="60"/>
-      <c r="J171" s="58" t="s">
+      <c r="H172" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="I172" s="60"/>
+      <c r="J172" s="58" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B173" s="61" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="61" t="s">
-        <v>343</v>
-      </c>
-      <c r="C172" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="D172" s="59" t="s">
+      <c r="C173" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D173" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="E172" s="58"/>
-      <c r="F172" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G172" s="55" t="n">
+      <c r="E173" s="58"/>
+      <c r="F173" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G173" s="55" t="n">
         <f aca="false">Sıcaklar!D69</f>
         <v>60</v>
       </c>
-      <c r="H172" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="I172" s="60"/>
-      <c r="J172" s="58" t="s">
+      <c r="H173" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="I173" s="60"/>
+      <c r="J173" s="58" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B174" s="61" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="61" t="s">
-        <v>343</v>
-      </c>
-      <c r="C173" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="D173" s="59" t="s">
+      <c r="C174" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D174" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="E173" s="58"/>
-      <c r="F173" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G173" s="55" t="n">
+      <c r="E174" s="58"/>
+      <c r="F174" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G174" s="55" t="n">
         <f aca="false">Sıcaklar!D70</f>
         <v>40</v>
       </c>
-      <c r="H173" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="I173" s="60"/>
-      <c r="J173" s="58" t="s">
+      <c r="H174" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="I174" s="60"/>
+      <c r="J174" s="58" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B175" s="61" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="61" t="s">
-        <v>343</v>
-      </c>
-      <c r="C174" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="D174" s="59" t="s">
+      <c r="C175" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D175" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="E174" s="58"/>
-      <c r="F174" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G174" s="55" t="n">
+      <c r="E175" s="58"/>
+      <c r="F175" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G175" s="55" t="n">
         <f aca="false">Soğuklar!D70</f>
         <v>60</v>
       </c>
-      <c r="H174" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="I174" s="60"/>
-      <c r="J174" s="58" t="s">
+      <c r="H175" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="I175" s="60"/>
+      <c r="J175" s="58" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B176" s="61" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="61" t="s">
-        <v>343</v>
-      </c>
-      <c r="C175" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="D175" s="59" t="s">
+      <c r="C176" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D176" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="E175" s="58"/>
-      <c r="F175" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G175" s="55" t="n">
+      <c r="E176" s="58"/>
+      <c r="F176" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G176" s="55" t="n">
         <f aca="false">Soğuklar!D71</f>
         <v>90</v>
       </c>
-      <c r="H175" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="I175" s="60"/>
-      <c r="J175" s="58" t="s">
+      <c r="H176" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="I176" s="60"/>
+      <c r="J176" s="58" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B177" s="61" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="61" t="s">
-        <v>343</v>
-      </c>
-      <c r="C176" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="D176" s="59" t="s">
+      <c r="C177" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D177" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="E176" s="58"/>
-      <c r="F176" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="G176" s="55" t="n">
+      <c r="E177" s="58"/>
+      <c r="F177" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="G177" s="55" t="n">
         <f aca="false">Soğuklar!D72</f>
         <v>60</v>
       </c>
-      <c r="H176" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="I176" s="60"/>
-      <c r="J176" s="58" t="s">
-        <v>346</v>
+      <c r="H177" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="I177" s="60"/>
+      <c r="J177" s="58" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:J176"/>
+  <autoFilter ref="B5:J177"/>
   <mergeCells count="2">
     <mergeCell ref="C1:J2"/>
     <mergeCell ref="B3:J3"/>

--- a/menu/Ciao_Fiyat_Listesi.xlsx
+++ b/menu/Ciao_Fiyat_Listesi.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="350">
   <si>
     <t xml:space="preserve">MENÜ FİYAT LİSTESİ</t>
   </si>
@@ -915,7 +915,7 @@
     <t xml:space="preserve">Fiyat Soğuklar sayfasından gelir</t>
   </si>
   <si>
-    <t xml:space="preserve">Bu ürünlerin hepsinin 8 × 5 cm fiyat etiketi vardır. Mavi rakamlar burada girilir; yeşil rakamlar Soğuklar sayfasından gelir.</t>
+    <t xml:space="preserve">Bu ürünlerin hepsinin 7 × 4 cm fiyat etiketi vardır. Mavi rakamlar burada girilir; yeşil rakamlar Soğuklar sayfasından gelir.</t>
   </si>
   <si>
     <t xml:space="preserve">TÜM ÜRÜNLER · POS</t>
@@ -1011,6 +1011,9 @@
     <t xml:space="preserve">Kasa (ekranda yok)</t>
   </si>
   <si>
+    <t xml:space="preserve">Var</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ciao Signature</t>
   </si>
   <si>
@@ -1045,9 +1048,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ekran 2 · Bar önü</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var</t>
   </si>
   <si>
     <t xml:space="preserve">Tatlılar</t>
@@ -10035,7 +10035,9 @@
       <c r="H59" s="58" t="s">
         <v>319</v>
       </c>
-      <c r="I59" s="60"/>
+      <c r="I59" s="60" t="s">
+        <v>325</v>
+      </c>
       <c r="J59" s="58"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10061,7 +10063,9 @@
       <c r="H60" s="58" t="s">
         <v>319</v>
       </c>
-      <c r="I60" s="60"/>
+      <c r="I60" s="60" t="s">
+        <v>325</v>
+      </c>
       <c r="J60" s="58"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10087,7 +10091,9 @@
       <c r="H61" s="58" t="s">
         <v>319</v>
       </c>
-      <c r="I61" s="60"/>
+      <c r="I61" s="60" t="s">
+        <v>325</v>
+      </c>
       <c r="J61" s="58"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10113,7 +10119,9 @@
       <c r="H62" s="58" t="s">
         <v>319</v>
       </c>
-      <c r="I62" s="60"/>
+      <c r="I62" s="60" t="s">
+        <v>325</v>
+      </c>
       <c r="J62" s="58"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10139,7 +10147,9 @@
       <c r="H63" s="58" t="s">
         <v>319</v>
       </c>
-      <c r="I63" s="60"/>
+      <c r="I63" s="60" t="s">
+        <v>325</v>
+      </c>
       <c r="J63" s="58"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10165,7 +10175,9 @@
       <c r="H64" s="58" t="s">
         <v>319</v>
       </c>
-      <c r="I64" s="60"/>
+      <c r="I64" s="60" t="s">
+        <v>325</v>
+      </c>
       <c r="J64" s="58"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10173,7 +10185,7 @@
         <v>317</v>
       </c>
       <c r="C65" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D65" s="59" t="s">
         <v>116</v>
@@ -10199,7 +10211,7 @@
         <v>317</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D66" s="59" t="s">
         <v>116</v>
@@ -10225,7 +10237,7 @@
         <v>317</v>
       </c>
       <c r="C67" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D67" s="59" t="s">
         <v>119</v>
@@ -10251,7 +10263,7 @@
         <v>317</v>
       </c>
       <c r="C68" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D68" s="59" t="s">
         <v>119</v>
@@ -10277,7 +10289,7 @@
         <v>317</v>
       </c>
       <c r="C69" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D69" s="59" t="s">
         <v>121</v>
@@ -10303,7 +10315,7 @@
         <v>317</v>
       </c>
       <c r="C70" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D70" s="59" t="s">
         <v>121</v>
@@ -10329,7 +10341,7 @@
         <v>317</v>
       </c>
       <c r="C71" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D71" s="59" t="s">
         <v>123</v>
@@ -10355,7 +10367,7 @@
         <v>317</v>
       </c>
       <c r="C72" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D72" s="59" t="s">
         <v>123</v>
@@ -10381,7 +10393,7 @@
         <v>317</v>
       </c>
       <c r="C73" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D73" s="59" t="s">
         <v>125</v>
@@ -10407,7 +10419,7 @@
         <v>317</v>
       </c>
       <c r="C74" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D74" s="59" t="s">
         <v>125</v>
@@ -10430,10 +10442,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="57" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C75" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D75" s="59" t="s">
         <v>137</v>
@@ -10449,17 +10461,17 @@
         <v>170</v>
       </c>
       <c r="H75" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I75" s="60"/>
       <c r="J75" s="58"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C76" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D76" s="59" t="s">
         <v>137</v>
@@ -10475,17 +10487,17 @@
         <v>190</v>
       </c>
       <c r="H76" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I76" s="60"/>
       <c r="J76" s="58"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C77" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D77" s="59" t="s">
         <v>139</v>
@@ -10501,17 +10513,17 @@
         <v>220</v>
       </c>
       <c r="H77" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I77" s="60"/>
       <c r="J77" s="58"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C78" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D78" s="59" t="s">
         <v>139</v>
@@ -10527,17 +10539,17 @@
         <v>240</v>
       </c>
       <c r="H78" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I78" s="60"/>
       <c r="J78" s="58"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C79" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D79" s="59" t="s">
         <v>141</v>
@@ -10553,17 +10565,17 @@
         <v>240</v>
       </c>
       <c r="H79" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I79" s="60"/>
       <c r="J79" s="58"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C80" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D80" s="59" t="s">
         <v>141</v>
@@ -10579,17 +10591,17 @@
         <v>260</v>
       </c>
       <c r="H80" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I80" s="60"/>
       <c r="J80" s="58"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C81" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D81" s="59" t="s">
         <v>143</v>
@@ -10605,17 +10617,17 @@
         <v>230</v>
       </c>
       <c r="H81" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I81" s="60"/>
       <c r="J81" s="58"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C82" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D82" s="59" t="s">
         <v>143</v>
@@ -10631,17 +10643,17 @@
         <v>250</v>
       </c>
       <c r="H82" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I82" s="60"/>
       <c r="J82" s="58"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C83" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D83" s="59" t="s">
         <v>145</v>
@@ -10657,17 +10669,17 @@
         <v>250</v>
       </c>
       <c r="H83" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I83" s="60"/>
       <c r="J83" s="58"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C84" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D84" s="59" t="s">
         <v>145</v>
@@ -10683,17 +10695,17 @@
         <v>280</v>
       </c>
       <c r="H84" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I84" s="60"/>
       <c r="J84" s="58"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C85" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D85" s="59" t="s">
         <v>147</v>
@@ -10709,17 +10721,17 @@
         <v>150</v>
       </c>
       <c r="H85" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I85" s="60"/>
       <c r="J85" s="58"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C86" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D86" s="59" t="s">
         <v>147</v>
@@ -10735,17 +10747,17 @@
         <v>170</v>
       </c>
       <c r="H86" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I86" s="60"/>
       <c r="J86" s="58"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C87" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D87" s="59" t="s">
         <v>149</v>
@@ -10761,17 +10773,17 @@
         <v>250</v>
       </c>
       <c r="H87" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I87" s="60"/>
       <c r="J87" s="58"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C88" s="58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D88" s="59" t="s">
         <v>149</v>
@@ -10787,17 +10799,17 @@
         <v>270</v>
       </c>
       <c r="H88" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I88" s="60"/>
       <c r="J88" s="58"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C89" s="58" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D89" s="59" t="s">
         <v>152</v>
@@ -10813,17 +10825,17 @@
         <v>150</v>
       </c>
       <c r="H89" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I89" s="60"/>
       <c r="J89" s="58"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C90" s="58" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D90" s="59" t="s">
         <v>152</v>
@@ -10839,17 +10851,17 @@
         <v>170</v>
       </c>
       <c r="H90" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I90" s="60"/>
       <c r="J90" s="58"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C91" s="58" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D91" s="59" t="s">
         <v>154</v>
@@ -10865,17 +10877,17 @@
         <v>170</v>
       </c>
       <c r="H91" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I91" s="60"/>
       <c r="J91" s="58"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C92" s="58" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D92" s="59" t="s">
         <v>154</v>
@@ -10891,14 +10903,14 @@
         <v>190</v>
       </c>
       <c r="H92" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I92" s="60"/>
       <c r="J92" s="58"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C93" s="58" t="s">
         <v>157</v>
@@ -10917,14 +10929,14 @@
         <v>170</v>
       </c>
       <c r="H93" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I93" s="60"/>
       <c r="J93" s="58"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C94" s="58" t="s">
         <v>157</v>
@@ -10943,17 +10955,17 @@
         <v>190</v>
       </c>
       <c r="H94" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I94" s="60"/>
       <c r="J94" s="58"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C95" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D95" s="59" t="s">
         <v>160</v>
@@ -10969,17 +10981,17 @@
         <v>250</v>
       </c>
       <c r="H95" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I95" s="60"/>
       <c r="J95" s="58"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C96" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D96" s="59" t="s">
         <v>160</v>
@@ -10995,17 +11007,17 @@
         <v>270</v>
       </c>
       <c r="H96" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I96" s="60"/>
       <c r="J96" s="58"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C97" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D97" s="59" t="s">
         <v>161</v>
@@ -11021,17 +11033,17 @@
         <v>250</v>
       </c>
       <c r="H97" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I97" s="60"/>
       <c r="J97" s="58"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C98" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D98" s="59" t="s">
         <v>161</v>
@@ -11047,17 +11059,17 @@
         <v>270</v>
       </c>
       <c r="H98" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I98" s="60"/>
       <c r="J98" s="58"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C99" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D99" s="59" t="s">
         <v>163</v>
@@ -11073,17 +11085,17 @@
         <v>250</v>
       </c>
       <c r="H99" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I99" s="60"/>
       <c r="J99" s="58"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C100" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D100" s="59" t="s">
         <v>163</v>
@@ -11099,17 +11111,17 @@
         <v>270</v>
       </c>
       <c r="H100" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I100" s="60"/>
       <c r="J100" s="58"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C101" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D101" s="59" t="s">
         <v>165</v>
@@ -11125,17 +11137,17 @@
         <v>240</v>
       </c>
       <c r="H101" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I101" s="60"/>
       <c r="J101" s="58"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C102" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D102" s="59" t="s">
         <v>165</v>
@@ -11151,17 +11163,17 @@
         <v>260</v>
       </c>
       <c r="H102" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I102" s="60"/>
       <c r="J102" s="58"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C103" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D103" s="59" t="s">
         <v>167</v>
@@ -11177,17 +11189,17 @@
         <v>260</v>
       </c>
       <c r="H103" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I103" s="60"/>
       <c r="J103" s="58"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C104" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D104" s="59" t="s">
         <v>167</v>
@@ -11203,17 +11215,17 @@
         <v>280</v>
       </c>
       <c r="H104" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I104" s="60"/>
       <c r="J104" s="58"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C105" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D105" s="59" t="s">
         <v>169</v>
@@ -11229,17 +11241,17 @@
         <v>300</v>
       </c>
       <c r="H105" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I105" s="60"/>
       <c r="J105" s="58"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C106" s="58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D106" s="59" t="s">
         <v>169</v>
@@ -11255,17 +11267,17 @@
         <v>340</v>
       </c>
       <c r="H106" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I106" s="60"/>
       <c r="J106" s="58"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C107" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D107" s="59" t="s">
         <v>172</v>
@@ -11281,17 +11293,17 @@
         <v>280</v>
       </c>
       <c r="H107" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I107" s="60"/>
       <c r="J107" s="58"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C108" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D108" s="59" t="s">
         <v>172</v>
@@ -11307,17 +11319,17 @@
         <v>300</v>
       </c>
       <c r="H108" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I108" s="60"/>
       <c r="J108" s="58"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C109" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D109" s="59" t="s">
         <v>174</v>
@@ -11333,17 +11345,17 @@
         <v>270</v>
       </c>
       <c r="H109" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I109" s="60"/>
       <c r="J109" s="58"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C110" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D110" s="59" t="s">
         <v>174</v>
@@ -11359,17 +11371,17 @@
         <v>290</v>
       </c>
       <c r="H110" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I110" s="60"/>
       <c r="J110" s="58"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C111" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D111" s="59" t="s">
         <v>176</v>
@@ -11385,17 +11397,17 @@
         <v>270</v>
       </c>
       <c r="H111" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I111" s="60"/>
       <c r="J111" s="58"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C112" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D112" s="59" t="s">
         <v>176</v>
@@ -11411,17 +11423,17 @@
         <v>290</v>
       </c>
       <c r="H112" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I112" s="60"/>
       <c r="J112" s="58"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C113" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D113" s="59" t="s">
         <v>178</v>
@@ -11437,17 +11449,17 @@
         <v>300</v>
       </c>
       <c r="H113" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I113" s="60"/>
       <c r="J113" s="58"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C114" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D114" s="59" t="s">
         <v>178</v>
@@ -11463,17 +11475,17 @@
         <v>320</v>
       </c>
       <c r="H114" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I114" s="60"/>
       <c r="J114" s="58"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C115" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D115" s="59" t="s">
         <v>180</v>
@@ -11489,17 +11501,17 @@
         <v>300</v>
       </c>
       <c r="H115" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I115" s="60"/>
       <c r="J115" s="58"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C116" s="58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D116" s="59" t="s">
         <v>180</v>
@@ -11515,17 +11527,17 @@
         <v>320</v>
       </c>
       <c r="H116" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I116" s="60"/>
       <c r="J116" s="58"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C117" s="58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D117" s="59" t="s">
         <v>183</v>
@@ -11541,17 +11553,17 @@
         <v>260</v>
       </c>
       <c r="H117" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I117" s="60"/>
       <c r="J117" s="58"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C118" s="58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D118" s="59" t="s">
         <v>183</v>
@@ -11567,17 +11579,17 @@
         <v>280</v>
       </c>
       <c r="H118" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I118" s="60"/>
       <c r="J118" s="58"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C119" s="58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D119" s="59" t="s">
         <v>185</v>
@@ -11593,17 +11605,17 @@
         <v>260</v>
       </c>
       <c r="H119" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I119" s="60"/>
       <c r="J119" s="58"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C120" s="58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D120" s="59" t="s">
         <v>185</v>
@@ -11619,17 +11631,17 @@
         <v>280</v>
       </c>
       <c r="H120" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I120" s="60"/>
       <c r="J120" s="58"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C121" s="58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D121" s="59" t="s">
         <v>186</v>
@@ -11645,17 +11657,17 @@
         <v>240</v>
       </c>
       <c r="H121" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I121" s="60"/>
       <c r="J121" s="58"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C122" s="58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D122" s="59" t="s">
         <v>186</v>
@@ -11671,17 +11683,17 @@
         <v>260</v>
       </c>
       <c r="H122" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I122" s="60"/>
       <c r="J122" s="58"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C123" s="58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D123" s="59" t="s">
         <v>188</v>
@@ -11697,17 +11709,17 @@
         <v>270</v>
       </c>
       <c r="H123" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I123" s="60"/>
       <c r="J123" s="58"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C124" s="58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D124" s="59" t="s">
         <v>188</v>
@@ -11723,17 +11735,17 @@
         <v>290</v>
       </c>
       <c r="H124" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I124" s="60"/>
       <c r="J124" s="58"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C125" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D125" s="59" t="s">
         <v>191</v>
@@ -11749,17 +11761,17 @@
         <v>300</v>
       </c>
       <c r="H125" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I125" s="60"/>
       <c r="J125" s="58"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C126" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D126" s="59" t="s">
         <v>191</v>
@@ -11775,17 +11787,17 @@
         <v>320</v>
       </c>
       <c r="H126" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I126" s="60"/>
       <c r="J126" s="58"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C127" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D127" s="59" t="s">
         <v>193</v>
@@ -11801,17 +11813,17 @@
         <v>330</v>
       </c>
       <c r="H127" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I127" s="60"/>
       <c r="J127" s="58"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C128" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D128" s="59" t="s">
         <v>193</v>
@@ -11827,17 +11839,17 @@
         <v>350</v>
       </c>
       <c r="H128" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I128" s="60"/>
       <c r="J128" s="58"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C129" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D129" s="59" t="s">
         <v>195</v>
@@ -11853,17 +11865,17 @@
         <v>290</v>
       </c>
       <c r="H129" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I129" s="60"/>
       <c r="J129" s="58"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C130" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D130" s="59" t="s">
         <v>195</v>
@@ -11879,17 +11891,17 @@
         <v>310</v>
       </c>
       <c r="H130" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I130" s="60"/>
       <c r="J130" s="58"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C131" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D131" s="59" t="s">
         <v>197</v>
@@ -11905,17 +11917,17 @@
         <v>290</v>
       </c>
       <c r="H131" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I131" s="60"/>
       <c r="J131" s="58"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C132" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D132" s="59" t="s">
         <v>197</v>
@@ -11931,17 +11943,17 @@
         <v>310</v>
       </c>
       <c r="H132" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I132" s="60"/>
       <c r="J132" s="58"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C133" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D133" s="59" t="s">
         <v>199</v>
@@ -11957,17 +11969,17 @@
         <v>290</v>
       </c>
       <c r="H133" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I133" s="60"/>
       <c r="J133" s="58"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C134" s="58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D134" s="59" t="s">
         <v>199</v>
@@ -11983,17 +11995,17 @@
         <v>310</v>
       </c>
       <c r="H134" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I134" s="60"/>
       <c r="J134" s="58"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C135" s="58" t="s">
         <v>326</v>
-      </c>
-      <c r="C135" s="58" t="s">
-        <v>325</v>
       </c>
       <c r="D135" s="59" t="s">
         <v>116</v>
@@ -12009,17 +12021,17 @@
         <v>300</v>
       </c>
       <c r="H135" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I135" s="60"/>
       <c r="J135" s="58"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C136" s="58" t="s">
         <v>326</v>
-      </c>
-      <c r="C136" s="58" t="s">
-        <v>325</v>
       </c>
       <c r="D136" s="59" t="s">
         <v>116</v>
@@ -12035,17 +12047,17 @@
         <v>320</v>
       </c>
       <c r="H136" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I136" s="60"/>
       <c r="J136" s="58"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C137" s="58" t="s">
         <v>326</v>
-      </c>
-      <c r="C137" s="58" t="s">
-        <v>325</v>
       </c>
       <c r="D137" s="59" t="s">
         <v>202</v>
@@ -12061,7 +12073,7 @@
         <v>280</v>
       </c>
       <c r="H137" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I137" s="60"/>
       <c r="J137" s="58" t="s">
@@ -12070,10 +12082,10 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C138" s="58" t="s">
         <v>326</v>
-      </c>
-      <c r="C138" s="58" t="s">
-        <v>325</v>
       </c>
       <c r="D138" s="59" t="s">
         <v>202</v>
@@ -12089,7 +12101,7 @@
         <v>300</v>
       </c>
       <c r="H138" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I138" s="60"/>
       <c r="J138" s="58" t="s">
@@ -12098,10 +12110,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C139" s="58" t="s">
         <v>326</v>
-      </c>
-      <c r="C139" s="58" t="s">
-        <v>325</v>
       </c>
       <c r="D139" s="59" t="s">
         <v>205</v>
@@ -12117,17 +12129,17 @@
         <v>180</v>
       </c>
       <c r="H139" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I139" s="60"/>
       <c r="J139" s="58"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C140" s="58" t="s">
         <v>326</v>
-      </c>
-      <c r="C140" s="58" t="s">
-        <v>325</v>
       </c>
       <c r="D140" s="59" t="s">
         <v>205</v>
@@ -12143,17 +12155,17 @@
         <v>200</v>
       </c>
       <c r="H140" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I140" s="60"/>
       <c r="J140" s="58"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C141" s="58" t="s">
         <v>326</v>
-      </c>
-      <c r="C141" s="58" t="s">
-        <v>325</v>
       </c>
       <c r="D141" s="59" t="s">
         <v>207</v>
@@ -12169,17 +12181,17 @@
         <v>180</v>
       </c>
       <c r="H141" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I141" s="60"/>
       <c r="J141" s="58"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C142" s="58" t="s">
         <v>326</v>
-      </c>
-      <c r="C142" s="58" t="s">
-        <v>325</v>
       </c>
       <c r="D142" s="59" t="s">
         <v>207</v>
@@ -12195,164 +12207,164 @@
         <v>200</v>
       </c>
       <c r="H142" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I142" s="60"/>
       <c r="J142" s="58"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="57" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C143" s="58" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D143" s="59" t="s">
         <v>210</v>
       </c>
       <c r="E143" s="58"/>
       <c r="F143" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G143" s="55" t="n">
         <f aca="false">IF(Soğuklar!D58="","",Soğuklar!D58)</f>
         <v>40</v>
       </c>
       <c r="H143" s="58" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I143" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J143" s="58"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C144" s="58" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D144" s="59" t="s">
         <v>211</v>
       </c>
       <c r="E144" s="58"/>
       <c r="F144" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G144" s="55" t="n">
         <f aca="false">IF(Soğuklar!D59="","",Soğuklar!D59)</f>
         <v>60</v>
       </c>
       <c r="H144" s="58" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I144" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J144" s="58"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C145" s="58" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D145" s="59" t="s">
         <v>212</v>
       </c>
       <c r="E145" s="58"/>
       <c r="F145" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G145" s="55" t="n">
         <f aca="false">IF(Soğuklar!D60="","",Soğuklar!D60)</f>
         <v>80</v>
       </c>
       <c r="H145" s="58" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I145" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J145" s="58"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C146" s="58" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D146" s="59" t="s">
         <v>213</v>
       </c>
       <c r="E146" s="58"/>
       <c r="F146" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G146" s="55" t="n">
         <f aca="false">IF(Soğuklar!D61="","",Soğuklar!D61)</f>
         <v>120</v>
       </c>
       <c r="H146" s="58" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I146" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J146" s="58"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C147" s="58" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D147" s="59" t="s">
         <v>214</v>
       </c>
       <c r="E147" s="58"/>
       <c r="F147" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G147" s="55" t="n">
         <f aca="false">IF(Soğuklar!D62="","",Soğuklar!D62)</f>
         <v>200</v>
       </c>
       <c r="H147" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I147" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J147" s="58"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C148" s="58" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D148" s="59" t="s">
         <v>215</v>
       </c>
       <c r="E148" s="58"/>
       <c r="F148" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G148" s="55" t="n">
         <f aca="false">IF(Soğuklar!D63="","",Soğuklar!D63)</f>
         <v>170</v>
       </c>
       <c r="H148" s="58" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I148" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J148" s="58"/>
     </row>
@@ -12370,7 +12382,7 @@
         <v>226</v>
       </c>
       <c r="F149" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G149" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E8="","",'Tatlı &amp; Atıştırmalık'!E8)</f>
@@ -12380,7 +12392,7 @@
         <v>340</v>
       </c>
       <c r="I149" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J149" s="58"/>
     </row>
@@ -12398,7 +12410,7 @@
         <v>229</v>
       </c>
       <c r="F150" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G150" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E9="","",'Tatlı &amp; Atıştırmalık'!E9)</f>
@@ -12408,7 +12420,7 @@
         <v>340</v>
       </c>
       <c r="I150" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J150" s="58"/>
     </row>
@@ -12426,7 +12438,7 @@
         <v>232</v>
       </c>
       <c r="F151" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G151" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E10="","",'Tatlı &amp; Atıştırmalık'!E10)</f>
@@ -12436,7 +12448,7 @@
         <v>340</v>
       </c>
       <c r="I151" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J151" s="58"/>
     </row>
@@ -12454,7 +12466,7 @@
         <v>235</v>
       </c>
       <c r="F152" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G152" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E11="","",'Tatlı &amp; Atıştırmalık'!E11)</f>
@@ -12464,7 +12476,7 @@
         <v>340</v>
       </c>
       <c r="I152" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J152" s="58"/>
     </row>
@@ -12482,7 +12494,7 @@
         <v>238</v>
       </c>
       <c r="F153" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G153" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E12="","",'Tatlı &amp; Atıştırmalık'!E12)</f>
@@ -12492,7 +12504,7 @@
         <v>340</v>
       </c>
       <c r="I153" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J153" s="58"/>
     </row>
@@ -12510,7 +12522,7 @@
         <v>241</v>
       </c>
       <c r="F154" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G154" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E13="","",'Tatlı &amp; Atıştırmalık'!E13)</f>
@@ -12520,7 +12532,7 @@
         <v>340</v>
       </c>
       <c r="I154" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J154" s="58"/>
     </row>
@@ -12538,7 +12550,7 @@
         <v>244</v>
       </c>
       <c r="F155" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G155" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E14="","",'Tatlı &amp; Atıştırmalık'!E14)</f>
@@ -12548,7 +12560,7 @@
         <v>340</v>
       </c>
       <c r="I155" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J155" s="58"/>
     </row>
@@ -12566,7 +12578,7 @@
         <v>247</v>
       </c>
       <c r="F156" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G156" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E15="","",'Tatlı &amp; Atıştırmalık'!E15)</f>
@@ -12576,7 +12588,7 @@
         <v>340</v>
       </c>
       <c r="I156" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J156" s="58"/>
     </row>
@@ -12594,7 +12606,7 @@
         <v>251</v>
       </c>
       <c r="F157" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G157" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E18="","",'Tatlı &amp; Atıştırmalık'!E18)</f>
@@ -12604,7 +12616,7 @@
         <v>340</v>
       </c>
       <c r="I157" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J157" s="58"/>
     </row>
@@ -12622,7 +12634,7 @@
         <v>254</v>
       </c>
       <c r="F158" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G158" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E19="","",'Tatlı &amp; Atıştırmalık'!E19)</f>
@@ -12632,7 +12644,7 @@
         <v>340</v>
       </c>
       <c r="I158" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J158" s="58"/>
     </row>
@@ -12650,7 +12662,7 @@
         <v>257</v>
       </c>
       <c r="F159" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G159" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E20="","",'Tatlı &amp; Atıştırmalık'!E20)</f>
@@ -12660,7 +12672,7 @@
         <v>340</v>
       </c>
       <c r="I159" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J159" s="58"/>
     </row>
@@ -12678,7 +12690,7 @@
         <v>260</v>
       </c>
       <c r="F160" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G160" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E21="","",'Tatlı &amp; Atıştırmalık'!E21)</f>
@@ -12688,7 +12700,7 @@
         <v>340</v>
       </c>
       <c r="I160" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J160" s="58"/>
     </row>
@@ -12706,7 +12718,7 @@
         <v>263</v>
       </c>
       <c r="F161" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G161" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E22="","",'Tatlı &amp; Atıştırmalık'!E22)</f>
@@ -12716,7 +12728,7 @@
         <v>340</v>
       </c>
       <c r="I161" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J161" s="58"/>
     </row>
@@ -12734,7 +12746,7 @@
         <v>267</v>
       </c>
       <c r="F162" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G162" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E25="","",'Tatlı &amp; Atıştırmalık'!E25)</f>
@@ -12744,7 +12756,7 @@
         <v>340</v>
       </c>
       <c r="I162" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J162" s="58"/>
     </row>
@@ -12762,7 +12774,7 @@
         <v>269</v>
       </c>
       <c r="F163" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G163" s="55" t="n">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E26="","",'Tatlı &amp; Atıştırmalık'!E26)</f>
@@ -12772,7 +12784,7 @@
         <v>340</v>
       </c>
       <c r="I163" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J163" s="58"/>
     </row>
@@ -12790,7 +12802,7 @@
         <v>272</v>
       </c>
       <c r="F164" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G164" s="55" t="str">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E29="","",'Tatlı &amp; Atıştırmalık'!E29)</f>
@@ -12818,7 +12830,7 @@
         <v>276</v>
       </c>
       <c r="F165" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G165" s="55" t="str">
         <f aca="false">IF('Tatlı &amp; Atıştırmalık'!E30="","",'Tatlı &amp; Atıştırmalık'!E30)</f>
@@ -12846,7 +12858,7 @@
         <v>282</v>
       </c>
       <c r="F166" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G166" s="55" t="n">
         <f aca="false">IF('Kasa Önü'!D8="","",'Kasa Önü'!D8)</f>
@@ -12856,7 +12868,7 @@
         <v>345</v>
       </c>
       <c r="I166" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J166" s="58" t="s">
         <v>283</v>
@@ -12876,7 +12888,7 @@
         <v>285</v>
       </c>
       <c r="F167" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G167" s="55" t="n">
         <f aca="false">IF('Kasa Önü'!D9="","",'Kasa Önü'!D9)</f>
@@ -12886,7 +12898,7 @@
         <v>345</v>
       </c>
       <c r="I167" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J167" s="58" t="s">
         <v>283</v>
@@ -12906,7 +12918,7 @@
         <v>287</v>
       </c>
       <c r="F168" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G168" s="55" t="n">
         <f aca="false">IF('Kasa Önü'!D10="","",'Kasa Önü'!D10)</f>
@@ -12916,7 +12928,7 @@
         <v>345</v>
       </c>
       <c r="I168" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J168" s="58" t="s">
         <v>283</v>
@@ -12936,7 +12948,7 @@
         <v>289</v>
       </c>
       <c r="F169" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G169" s="55" t="n">
         <f aca="false">IF('Kasa Önü'!D11="","",'Kasa Önü'!D11)</f>
@@ -12946,7 +12958,7 @@
         <v>345</v>
       </c>
       <c r="I169" s="60" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="J169" s="58" t="s">
         <v>283</v>
@@ -12964,7 +12976,7 @@
       </c>
       <c r="E170" s="58"/>
       <c r="F170" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G170" s="55" t="n">
         <f aca="false">Sıcaklar!D66</f>
@@ -12990,7 +13002,7 @@
       </c>
       <c r="E171" s="58"/>
       <c r="F171" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G171" s="55" t="n">
         <f aca="false">Sıcaklar!D67</f>
@@ -13016,7 +13028,7 @@
       </c>
       <c r="E172" s="58"/>
       <c r="F172" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G172" s="55" t="n">
         <f aca="false">Sıcaklar!D68</f>
@@ -13042,7 +13054,7 @@
       </c>
       <c r="E173" s="58"/>
       <c r="F173" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G173" s="55" t="n">
         <f aca="false">Sıcaklar!D69</f>
@@ -13068,7 +13080,7 @@
       </c>
       <c r="E174" s="58"/>
       <c r="F174" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G174" s="55" t="n">
         <f aca="false">Sıcaklar!D70</f>
@@ -13094,7 +13106,7 @@
       </c>
       <c r="E175" s="58"/>
       <c r="F175" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G175" s="55" t="n">
         <f aca="false">Soğuklar!D70</f>
@@ -13120,7 +13132,7 @@
       </c>
       <c r="E176" s="58"/>
       <c r="F176" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G176" s="55" t="n">
         <f aca="false">Soğuklar!D71</f>
@@ -13146,7 +13158,7 @@
       </c>
       <c r="E177" s="58"/>
       <c r="F177" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G177" s="55" t="n">
         <f aca="false">Soğuklar!D72</f>
